--- a/GearSage-client/pkgGear/data_raw/abu_baitcasting_reel_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/abu_baitcasting_reel_import.xlsx
@@ -488,13 +488,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Black%20Max%E2%84%A2%20Baitcast%20Reel_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>基础入门主力</v>
       </c>
       <c r="M2" t="str">
         <v>The Black Max low profile baitcast reel is engineered with class-leading performance in a compact, lightweight design. A graphite frame and body, along with the compact bent handle and drag star, provide a more ergonomic feel for all-day fishing sessions. The result is proven value and reliability that anglers have come to expect from this series.</v>
@@ -512,10 +512,10 @@
         <v/>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>入门泛用路亚</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>价格友好 / 结构简单 / 日常泛用</v>
       </c>
     </row>
     <row r="3">
@@ -547,13 +547,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20SX%20Flipping%20Switch%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>入门重障碍主力</v>
       </c>
       <c r="M3" t="str">
         <v>Abu Garcia Max SX Flipping Switch LP reels flow down technology from the Revo 5 platform into a LP platform that offers performance reels at a great price point. The Max SX Casting Reels expand the trusted legacy of the Max LP family with a design that offers a new a-sym frame design along and upgraded drag systems. An aluminum 90mm bent handle is furnished with co-molded soft touch knobs to provide a comfortable grip and buttery smooth retrieve.</v>
@@ -571,10 +571,10 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v/>
+        <v>flipping / pitching / cover</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>翻转开关 / 近岸重障碍 / 入门重装</v>
       </c>
     </row>
     <row r="4">
@@ -606,13 +606,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20SX%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>入门进阶主力</v>
       </c>
       <c r="M4" t="str">
         <v>Abu Garcia Max SX LP reels flow down technology from the Revo 5 platform into a LP platform that offers performance reels at a great price point. The Max SX Casting Reels expand the trusted legacy of the Max LP family with a design that offers a new a-sym frame design along and upgraded drag systems. An aluminum 90mm bent handle is furnished with co-molded soft touch knobs to provide a comfortable grip and buttery smooth retrieve.</v>
@@ -630,10 +630,10 @@
         <v/>
       </c>
       <c r="R4" t="str">
-        <v/>
+        <v>淡水泛用路亚</v>
       </c>
       <c r="S4" t="str">
-        <v/>
+        <v>低姿态易上手 / 日常泛用 / 性价比明确</v>
       </c>
     </row>
     <row r="5">
@@ -665,13 +665,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20Pro%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>入门进阶主力</v>
       </c>
       <c r="M5" t="str">
         <v>Abu Garcia Max Pro LP reels flow down technology from the Revo 5 platform into a LP platform that offers performance reels at a great price point. The Max Pro Casting Reels expand the trusted legacy of the Max LP family with a design that offers a new a-sym frame design along and upgraded carbon drag systems. An aluminum 90mm bent handle is furnished with oversized co-molded soft touch knobs to provide a comfortable grip and buttery smooth retrieve.</v>
@@ -689,10 +689,10 @@
         <v/>
       </c>
       <c r="R5" t="str">
-        <v/>
+        <v>淡水泛用路亚</v>
       </c>
       <c r="S5" t="str">
-        <v/>
+        <v>低姿态易上手 / 日常泛用 / 性价比明确</v>
       </c>
     </row>
     <row r="6">
@@ -724,13 +724,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20SX%20Winch%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>入门低速卷阻主力</v>
       </c>
       <c r="M6" t="str">
         <v>Abu Garcia Max SX Winch LP reels flow down technology from the Revo 5 platform into a LP platform that offers performance reels at a great price point. The Max SX Winch casting reels expand the trusted legacy of the Max LP family with a design that offers a new a-sym frame design along and upgraded drag systems. An aluminum 90mm bent handle is furnished with co-molded soft touch knobs to provide a comfortable grip and buttery smooth retrieve. This reel has been purpose designed for anglers who fish crankbaits and moving baits.</v>
@@ -748,10 +748,10 @@
         <v/>
       </c>
       <c r="R6" t="str">
-        <v/>
+        <v>crankbait / moving bait</v>
       </c>
       <c r="S6" t="str">
-        <v/>
+        <v>低速比 / 慢收稳定 / moving bait 友好</v>
       </c>
     </row>
     <row r="7">
@@ -783,13 +783,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20Elite%20Rocket%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>Max高速搜索主力</v>
       </c>
       <c r="M7" t="str">
         <v>Abu Garcia Max Elite LP reels flow down technology from the Revo 5 platform into a LP platform that offers performance reels at a great price point. The Max Elite Casting Reels expand the trusted legacy of the Max LP family with a design that offers a new a-sym frame design along and upgraded carbon drag systems. An aluminum 90mm bent handle is furnished with oversized co-molded soft touch knobs to provide a comfortable grip and buttery smooth retrieve. The Max Elite Rocket features a 9.0:1gear ratio making it perfect for anglers who need ultra high-speed retrieves</v>
@@ -807,10 +807,10 @@
         <v/>
       </c>
       <c r="R7" t="str">
-        <v/>
+        <v>高速搜索取向</v>
       </c>
       <c r="S7" t="str">
-        <v/>
+        <v>9.0 高速比 / 快速回线 / search bait 友好</v>
       </c>
     </row>
     <row r="8">
@@ -842,13 +842,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20Predator%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>重载大饵主力</v>
       </c>
       <c r="M8" t="str">
         <v>The new Abu Garcia Max™ Predator LP reels have been specifically designed for anglers who are fishing with big baits targeting large fish. Designed with larger line capacity and high max drags, the Max™ Predator series is also available in a series of combos to give anglers a balanced outfit that has been perfectly matched to target everything from Bass to Muskie fishing.</v>
@@ -866,10 +866,10 @@
         <v/>
       </c>
       <c r="R8" t="str">
-        <v/>
+        <v>big bait / large fish</v>
       </c>
       <c r="S8" t="str">
-        <v/>
+        <v>大线杯 / 高拖力 / 大鱼和大饵取向</v>
       </c>
     </row>
     <row r="9">
@@ -901,13 +901,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Beast%E2%84%A2%20300%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>重载大饵旗舰</v>
       </c>
       <c r="M9" t="str">
         <v>Designed for cranking power, drag performance and durability, the Beast™ 300 series has been completely redesigned to give anglers a large format LP reel that is easy to palm, giving anglers more fish stopping power than any other reel in this class. Designed for anglers throwing A-Rigs and swimbaits up to 8 inches.</v>
@@ -925,10 +925,10 @@
         <v/>
       </c>
       <c r="R9" t="str">
-        <v/>
+        <v>A-rig / swimbait / 大型鱼</v>
       </c>
       <c r="S9" t="str">
-        <v/>
+        <v>30lb 拖力 / 大型低姿态 / 8英寸级 swimbait 取向</v>
       </c>
     </row>
     <row r="10">
@@ -960,13 +960,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Beast%E2%84%A2%20200%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>重载大饵主力</v>
       </c>
       <c r="M10" t="str">
         <v>Designed for cranking power, drag performance and durability, the Beast™ 200 series has been completely redesigned to give anglers a large format LP reel that is easy to palm, giving anglers more fish stopping power than any other reel in this class. Perfect for swimbaits up to 6 inches in length.</v>
@@ -984,10 +984,10 @@
         <v/>
       </c>
       <c r="R10" t="str">
-        <v/>
+        <v>swimbait / heavy duty</v>
       </c>
       <c r="S10" t="str">
-        <v/>
+        <v>大拖力 / 易掌握 / 6英寸级 swimbait 取向</v>
       </c>
     </row>
     <row r="11">
@@ -1019,13 +1019,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20X%20BFS%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>BFS 精细特化</v>
       </c>
       <c r="M11" t="str">
         <v>Delivering exceptional BFS performance the Revo X BFS features a lightweight BFS concept spool and BFS tuned MagTrax braking system that allows anglers to efficiently present ultra-lightweight lures. Built on an ergonomic asymmetric C6 carbon frame, the Revo X BFS is lightweight, without sacrificing durability.</v>
@@ -1043,10 +1043,10 @@
         <v/>
       </c>
       <c r="R11" t="str">
-        <v/>
+        <v>超轻饵精细玩法</v>
       </c>
       <c r="S11" t="str">
-        <v/>
+        <v>浅线杯 / 轻量刹车 / 轻饵抛投效率高</v>
       </c>
     </row>
     <row r="12">
@@ -1078,13 +1078,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ike%20Signature%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>签名竞技主力</v>
       </c>
       <c r="M12" t="str">
         <v>The Ike Signature Low Profile Reels have been precisely developed with Mike Iaconelli to achieve top tier performance for a wide variety techniques. Featuring a lightweight graphite frame, 8+1 stainless steel bearings, and Carbon Matrix drag with a drag clicker, the Ike Signature Low Profile Reel is built for reliable performance.</v>
@@ -1102,10 +1102,10 @@
         <v/>
       </c>
       <c r="R12" t="str">
-        <v/>
+        <v>泛用竞技取向</v>
       </c>
       <c r="S12" t="str">
-        <v/>
+        <v>Mike Iaconelli 签名 / 泛用覆盖广 / 竞技感明确</v>
       </c>
     </row>
     <row r="13">
@@ -1137,13 +1137,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20Inshore%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>近海主力</v>
       </c>
       <c r="M13" t="str">
         <v>Designed with the inshore angler in mind, the Revo® Inshore low profile baitcast reel features an ergonomic, asymmetric X2- Cräftic™ frame for added corrosion protection and High Performance Corrosion Resistant (HPCR®) bearings that provide maximum protection under the harshest conditions. Featuring an 95mm aluminum handle with large EVA knobs, the Revo Inshore fishing reel provides plenty of torque when fighting large inshore fish species. The Duragear™ D2 Gear Design™ provides a extremely powerful and durable gear system.</v>
@@ -1161,10 +1161,10 @@
         <v/>
       </c>
       <c r="R13" t="str">
-        <v/>
+        <v>inshore / 轻近海</v>
       </c>
       <c r="S13" t="str">
-        <v/>
+        <v>耐腐蚀 / 大型 EVA 握丸 / 近海大扭矩</v>
       </c>
     </row>
     <row r="14">
@@ -1196,13 +1196,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Zenon%E2%84%A2%20LTX%20BFS%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>BFS 精细特化</v>
       </c>
       <c r="M14" t="str">
         <v>Setting the standard in Bait Finesse performance the Zenon LTX-BFS has been designed and optimized for ultra-lightweight techniques. The Zenon LTX-BFS boasts a wide array of features including 9+1 stainless steel HPCR bearings, X2-Cräftic™ alloy frame, and aircraft-grade aluminum main gear. The Super Lightweight BFS Concept Spool and MagTrax braking system that has been tuned for BFS techniques ensure superior performance with lightweight lures.</v>
@@ -1220,10 +1220,10 @@
         <v/>
       </c>
       <c r="R14" t="str">
-        <v/>
+        <v>超轻饵精细玩法</v>
       </c>
       <c r="S14" t="str">
-        <v/>
+        <v>浅线杯 / 轻量刹车 / 轻饵抛投效率高</v>
       </c>
     </row>
     <row r="15">
@@ -1255,13 +1255,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20SX-SS%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>跳投障碍高端主力</v>
       </c>
       <c r="M15" t="str">
         <v>Redesigned from the ground up, the 5th generation of Revo low profile reels have been designed to provide best-in-class precision, power, and performance. Engineered to be the premier skipping, pitching and flipping reel in the Revo line, the Revo SX-SS features a lightweight shallow spool design and EXD Concept Design maximizes casting performance while our IVCB-6 braking system gives anglers ultimate control with nearly limitless braking options. The Revo SX-SS also features an asymmetrical body design and X2-Cräftic™ alloy frame for the ultimate balance in weight, strength and ergonomics. Driven by a super high speed 8.1:1 gear ratio and 22lbs of Power Stack Carbon Matrix Drag and 90mm bowed aluminum handle , the Revo SX-SS has the torque and power to haul any bass out of the thickest cover.</v>
@@ -1279,10 +1279,10 @@
         <v/>
       </c>
       <c r="R15" t="str">
-        <v/>
+        <v>skipping / pitching / flipping</v>
       </c>
       <c r="S15" t="str">
-        <v/>
+        <v>浅线杯 / skipping 特化 / 重障碍控线更强</v>
       </c>
     </row>
     <row r="16">
@@ -1314,13 +1314,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20X%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>全能主力</v>
       </c>
       <c r="M16" t="str">
         <v>Redesigned from the ground up, the 5th generation of Revo low profile reels have been designed to provide best-in-class precision, power, and performance. The Revo X low profile reel features a C6 Carbon frame and asymestrical body to optimize, weight, balance and ergonomics. Consistent brake pressure is delivered by the MagTrax™ brake system while the Carbon Matrix™ drag system provides 20lbs of super smooth reliable drag performance.</v>
@@ -1338,10 +1338,10 @@
         <v/>
       </c>
       <c r="R16" t="str">
-        <v/>
+        <v>淡水泛用主力</v>
       </c>
       <c r="S16" t="str">
-        <v/>
+        <v>C6 碳框 / 综合性能均衡 / 适用面广</v>
       </c>
     </row>
     <row r="17">
@@ -1373,13 +1373,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20SX%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>中高端全能主力</v>
       </c>
       <c r="M17" t="str">
         <v>Redesigned from the ground up, the 5th generation of Revo low profile reels have been designed to provide best-in-class precision, power, and performance. The Revo SX features our X2-Cräftic™ alloy frame and asymetrical body design to provide the ultimate balance in weight, strength, and ergonomics. With our D2 Gear design and up to 25lbs of Power Stack Carbon Matrix drag, the Revo SX has the torque and power you need in a workhorse reel. The EXD Concept design allows anglers to maximize their casting performance while our IVCB-6 braking system gives anglers ultimate control with nearly limitless braking options.</v>
@@ -1397,10 +1397,10 @@
         <v/>
       </c>
       <c r="R17" t="str">
-        <v/>
+        <v>泛用竞技 / 鲈鱼主力</v>
       </c>
       <c r="S17" t="str">
-        <v/>
+        <v>X2-Cräftic 框架 / 高拖力 / 全能 workhorse</v>
       </c>
     </row>
     <row r="18">
@@ -1432,13 +1432,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20STX%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>高端全能主力</v>
       </c>
       <c r="M18" t="str">
         <v>Redesigned from the ground up, the 5th generation of Revo low profile reels have been designed to provide best-in-class precision, power, and performance. The Revo STX features an asymetrical body design as well as our X2-Cräftic™ alloy frame and sideplate to provide the ultimate balance in weight, strength, and ergonomics. The EXD Concept design allows anglers to maximize their casting performance while our IVCB-6 braking system gives anglers ultimate control with nearly limitless braking options. With our D2 Gear design and up to 25lbs of Power Stack Carbon Matrix drag, the Revo STX has the torque and power you need in a workhorse reel.</v>
@@ -1456,10 +1456,10 @@
         <v/>
       </c>
       <c r="R18" t="str">
-        <v/>
+        <v>精度与力量兼顾</v>
       </c>
       <c r="S18" t="str">
-        <v/>
+        <v>铝框 + 侧板 / 高拖力 / 刹车调校空间大</v>
       </c>
     </row>
     <row r="19">
@@ -1491,13 +1491,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20Rocket%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>高速搜索主力</v>
       </c>
       <c r="M19" t="str">
         <v>Redesigned from the ground up, the 5th generation of Revo low profile reels have been designed to provide best-in-class precision, power, and performance. The Revo Rocket features an asymetric body design and our X2-Cräftic™ alloy frame and sideplate to provide the ultimate balance in weight, strength, and ergonomics. The EXD Concept design allows anglers to maximize their casting performance. Anglers have ultimate control with nearly limitless braking options thanks to our IVCB-6 braking system. With 18lbs of Power Stack Carbon Matrix drag and a blazing fast 10.1:1 gear ratio, the Revo Rocket excels at techniques such as topwater, flipping, and any other technique where speed is key. With a 95mm straight carbon handle and D2 Gear System, the Revo Rocket boasts more than enough torque and power to get the fiercest bass in.</v>
@@ -1515,10 +1515,10 @@
         <v/>
       </c>
       <c r="R19" t="str">
-        <v/>
+        <v>快节奏搜索取向</v>
       </c>
       <c r="S19" t="str">
-        <v/>
+        <v>超高速比 / 快速回线 / search bait 友好</v>
       </c>
     </row>
     <row r="20">
@@ -1550,13 +1550,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20SX%20Rocket%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>高速搜索主力</v>
       </c>
       <c r="M20" t="str">
         <v>Redesigned from the ground up, the 5th generation of Revo low profile reels have been designed to provide best-in-class precision, power, and performance. The Revo SX RKT features an asymmetrical body design and our X2-Cräftic™ alloy frame and sideplate to provide the ultimate balance in weight, strength, and ergonomics. The EXD Concept design allows anglers to maximize their casting performance while our IVCB-6 braking system gives anglers ultimate control with nearly limitless braking options. With 18lbs of Power Stack Carbon Matrix drag and a blazing fast 9.0:1 gear ratio, the SX RKT excels at techniques such as topwater, flipping, and any other technique where speed is key.</v>
@@ -1574,10 +1574,10 @@
         <v/>
       </c>
       <c r="R20" t="str">
-        <v/>
+        <v>快节奏搜索取向</v>
       </c>
       <c r="S20" t="str">
-        <v/>
+        <v>超高速比 / 快速回线 / search bait 友好</v>
       </c>
     </row>
     <row r="21">
@@ -1609,13 +1609,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20DLC_main.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>入门计数器主力</v>
       </c>
       <c r="M21" t="str">
         <v>Value-packed with power and performance, the Max Digital Line-Counter low profile reel gets the job done day after day. Featuring 5 stainless steel ball bearings for smooth operation, 20 pounds of drag pressure, and a lighted digital line-counter, this reel provides accuracy and power for a variety of situations. The addition of a bent handle and drag star translates into a more ergonomic feel for all day comfort.</v>
@@ -1633,10 +1633,10 @@
         <v/>
       </c>
       <c r="R21" t="str">
-        <v/>
+        <v>船钓 / 拖钓 / 深水</v>
       </c>
       <c r="S21" t="str">
-        <v/>
+        <v>数字计米 / DTT 警报 / 稳定实用</v>
       </c>
     </row>
     <row r="22">
@@ -1668,13 +1668,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20Toro%20DLC_main.jpg</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>入门计数器主力</v>
       </c>
       <c r="M22" t="str">
         <v>Value-packed with power and performance, the Max Toro Digital Line-Counter low profile reel gets the job done day after day. Featuring 5 stainless steel ball bearings for smooth operation, 20 pounds of drag pressure, and a lighted digital line-counter, this reel provides accuracy and power for a variety of situations. The addition of a bent handle and drag star translates into a more ergonomic feel for all day comfort.</v>
@@ -1692,10 +1692,10 @@
         <v/>
       </c>
       <c r="R22" t="str">
-        <v/>
+        <v>船钓 / 拖钓 / 深水</v>
       </c>
       <c r="S22" t="str">
-        <v/>
+        <v>数字计米 / DTT 警报 / 稳定实用</v>
       </c>
     </row>
     <row r="23">
@@ -1727,13 +1727,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Zenon%E2%84%A2%20MG-LTX%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>超轻精细旗舰</v>
       </c>
       <c r="M23" t="str">
         <v>Introducing Abu Garcia’s lightest, most compact low profile baitcast reel, the Abu Garcia® Zenon™ MG-LTX. Weighing in at just 4.5 ounces, the Zenon® MG-LTX low profile reel combines the new SLC spool concept with hybrid ceramic bearings, resulting in the ultimate finesse reel that has world class performance in a package that weighs almost nothing in the hand.</v>
@@ -1751,10 +1751,10 @@
         <v/>
       </c>
       <c r="R23" t="str">
-        <v/>
+        <v>高端 finesse</v>
       </c>
       <c r="S23" t="str">
-        <v/>
+        <v>4.5oz 超轻 / 精细抛投 / 高端手感取向</v>
       </c>
     </row>
     <row r="24">
@@ -1786,13 +1786,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Zenon%E2%84%A2%20X%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>轻量全能高端</v>
       </c>
       <c r="M24" t="str">
         <v>Engineered to give anglers the compact performance of the Zenon® MG-X along with the versatility of a heavy-duty fishing reel, the Zenon® X low profile reel features an aluminum frame for added strength and C6 carbon side plates and an aluminum main gear for maximum weight optimization. Easily adjustable and ultra compact, the Zenon®X is suited to throw anything from lightweight finesse baits all the way to heavy jigs.</v>
@@ -1810,10 +1810,10 @@
         <v/>
       </c>
       <c r="R24" t="str">
-        <v/>
+        <v>轻量到重饵泛用</v>
       </c>
       <c r="S24" t="str">
-        <v/>
+        <v>紧凑机身 / 铝主齿 / 轻重饵跨度大</v>
       </c>
     </row>
     <row r="25">
@@ -1845,13 +1845,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%204%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>入门进阶主力</v>
       </c>
       <c r="M25" t="str">
         <v>Built for heavy duty applications, the Max 40 and 60 large platform low profile reels have all the trusted legacy of the Max LP family with the addtion of larger line capacities, upgraged drags, and bait clickers.</v>
@@ -1869,10 +1869,10 @@
         <v/>
       </c>
       <c r="R25" t="str">
-        <v/>
+        <v>淡水泛用路亚</v>
       </c>
       <c r="S25" t="str">
-        <v/>
+        <v>低姿态易上手 / 日常泛用 / 性价比明确</v>
       </c>
     </row>
     <row r="26">
@@ -1904,13 +1904,13 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20X%20Low%20Profile%20Reel_main.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>入门进阶主力</v>
       </c>
       <c r="M26" t="str">
         <v>Abu Garcia Max X LP reels flow down technology from the Revo 5 platform into a LP platform that offers performance reels at a great price point. The Max X Casting Reels expand the trusted legacy of the Max LP family with a design that offers a new a-sym frame design and upgraded drag systems. An aluminum 90mm bent handle is furnished with co-molded soft touch knobs to provide a comfortable grip and buttery smooth retrieve.</v>
@@ -1928,10 +1928,10 @@
         <v/>
       </c>
       <c r="R26" t="str">
-        <v/>
+        <v>淡水泛用路亚</v>
       </c>
       <c r="S26" t="str">
-        <v/>
+        <v>低姿态易上手 / 日常泛用 / 性价比明确</v>
       </c>
     </row>
     <row r="27">
@@ -1957,19 +1957,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H27" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I27" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/C3%20Striper%20Special%20Round%20Reel_main.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>条纹鲈大物主力</v>
       </c>
       <c r="M27" t="str">
         <v>Born from the round reel platform, the Ambassadeur® Striper Special fishing reel offers anglers a unique package backed with proven components designed with striper fishing in mind. Performance starts with 3 stainless steel ball bearings + 1 roller bearing system and a smooth and consistent Carbon Matrix™ drag system. The 6-pin centrifugal brake delivers controlled casting while the extended bent handle with power knob gives anglers additional torque and power for hard-pulling fish. The synchronized level wind system ensures even line lay and a smooth retrieve.</v>
@@ -1987,10 +1987,10 @@
         <v/>
       </c>
       <c r="R27" t="str">
-        <v/>
+        <v>striper / 淡海水大物</v>
       </c>
       <c r="S27" t="str">
-        <v/>
+        <v>鼓轮大扭矩 / 强拖力 / striper 取向</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2016,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H28" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I28" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20Carp%20Pro%20Reel_main.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>鲤鱼大物主力</v>
       </c>
       <c r="M28" t="str">
         <v>A continued tradition of Swedish craftsmanship and design, the Ambassadeur® Carp Pro round baitcast reel features a six-pin centrifugal braking system and robust aluminum construction; the Carp Pro delivers superior casting performance and rock-solid durability.</v>
@@ -2046,10 +2046,10 @@
         <v/>
       </c>
       <c r="R28" t="str">
-        <v/>
+        <v>carp / 淡水大物</v>
       </c>
       <c r="S28" t="str">
-        <v/>
+        <v>鼓轮经典结构 / 长线容量 / 大物持久战</v>
       </c>
     </row>
     <row r="29">
@@ -2075,19 +2075,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H29" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I29" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/C3%20Carp%20Special%20Round%20Reel_main.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>鲤鱼大物主力</v>
       </c>
       <c r="M29" t="str">
         <v>Born from the C3 round reel platform, the Ambassadeur® Carp Special fishing reel offers anglers a unique package backed with proven components designed specifically for Carp fishing. Performance starts with 3 stainless steel ball bearings + 1 roller bearing system and a smooth and consistent Carbon Matrix™ drag system. The 6-pin centrifugal brake delivers controlled casting while the extended bent handle with power knob gives anglers additional torque and power for hard-pulling fish. The synchronized level wind system ensures even line lay and a smooth retrieve.</v>
@@ -2105,10 +2105,10 @@
         <v/>
       </c>
       <c r="R29" t="str">
-        <v/>
+        <v>carp / 淡水大物</v>
       </c>
       <c r="S29" t="str">
-        <v/>
+        <v>鼓轮经典结构 / 长线容量 / 大物持久战</v>
       </c>
     </row>
     <row r="30">
@@ -2134,19 +2134,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H30" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I30" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/C3%20Catfish%20Special%20Round%20Reel_main.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>鲶鱼大物主力</v>
       </c>
       <c r="M30" t="str">
         <v>Born from the C3 round reel platform, the Ambassadeur® Catfish Special fishing reel offers anglers a unique package backed with proven components designed specifically for catfish fishing. Performance starts with 3 stainless steel ball bearings + 1 roller bearing system and a smooth and consistent Carbon Matrix™ drag system. The 6-pin centrifugal brake delivers controlled casting while the extended bent handle with power knob gives anglers additional torque and power for hard-pulling fish. The synchronized level wind system ensures even line lay and a smooth retrieve. Custom color and graphics.</v>
@@ -2164,10 +2164,10 @@
         <v/>
       </c>
       <c r="R30" t="str">
-        <v/>
+        <v>catfish / 淡水大物</v>
       </c>
       <c r="S30" t="str">
-        <v/>
+        <v>扭矩稳定 / 大线容量 / 鲶鱼实战取向</v>
       </c>
     </row>
     <row r="31">
@@ -2193,19 +2193,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H31" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I31" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20Catfish%20Pro%20Reel_main.jpg</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>鲶鱼大物主力</v>
       </c>
       <c r="M31" t="str">
         <v>A continued tradition of Swedish craftsmanship and design, the Ambassadeur® Catfish Pro round baitcast reel features a six-pin centrifugal braking system and robust aluminum construction; the Catfish Pro delivers superior casting performance and rock-solid durability.</v>
@@ -2223,10 +2223,10 @@
         <v/>
       </c>
       <c r="R31" t="str">
-        <v/>
+        <v>catfish / 淡水大物</v>
       </c>
       <c r="S31" t="str">
-        <v/>
+        <v>扭矩稳定 / 大线容量 / 鲶鱼实战取向</v>
       </c>
     </row>
     <row r="32">
@@ -2252,19 +2252,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H32" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I32" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20S%20Line%20Counter_main.jpg</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K32" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>经典计数器主力</v>
       </c>
       <c r="M32" t="str">
         <v>Value-packed with power and performance, the Ambassadeur® S Line-Counter round reel gets the job done day after day. Featuring 2 stainless steel ball bearings for smooth operation, 11 pounds of drag pressure, and a lighted digital line-counter, this reel provides accuracy and power for a variety of situations. The addition of a bent handle and drag star translates into a more ergonomic feel for all day comfort.</v>
@@ -2282,10 +2282,10 @@
         <v/>
       </c>
       <c r="R32" t="str">
-        <v/>
+        <v>拖钓 / 深水 / 船钓</v>
       </c>
       <c r="S32" t="str">
-        <v/>
+        <v>机械或数字计数 / 稳定大物取向 / 船钓友好</v>
       </c>
     </row>
     <row r="33">
@@ -2311,19 +2311,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H33" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I33" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20Pro%20Rocket%20BE_main.jpg</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K33" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L33" t="str">
-        <v/>
+        <v>远投大物主力</v>
       </c>
       <c r="M33" t="str">
         <v>A continued tradition of Swedish craftsmanship and design, the Ambassadeur® Black edition round baitcast reel is now available in additional sizes. Featuring a six-pin centrifugal braking system and a robust aluminum construction, the international best seller delivers superior casting performance and rock-solid durability.</v>
@@ -2341,10 +2341,10 @@
         <v/>
       </c>
       <c r="R33" t="str">
-        <v/>
+        <v>远投 / 大水面大物</v>
       </c>
       <c r="S33" t="str">
-        <v/>
+        <v>长投能力强 / 鼓轮经典结构 / 大水面取向</v>
       </c>
     </row>
     <row r="34">
@@ -2370,19 +2370,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H34" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I34" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20CS%20Pro%20Rocket_main.jpg</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K34" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L34" t="str">
-        <v/>
+        <v>远投大物主力</v>
       </c>
       <c r="M34" t="str">
         <v>The Ambassadeur® CS Pro Rocket round baitcast reel is an international best seller. Engineered for super long castability, this model also features a synchronized level wind system for even line lay. The Carbon Matrix™ Drag system included in this reel is our strongest and most durable drag system available. The updated extended bent handle with power knob gives anglers an edge by increasing torque and aligning the cranking hand closer to the reel for more efficient fighting power. Durable components, including 2 stainless steel ball bearings + 1 roller bearing, a Duragear™ brass gear ,and a corrosion-resistant instant anti-reverse bearing ensure dependability for the long haul.</v>
@@ -2400,10 +2400,10 @@
         <v/>
       </c>
       <c r="R34" t="str">
-        <v/>
+        <v>远投 / 大水面大物</v>
       </c>
       <c r="S34" t="str">
-        <v/>
+        <v>长投能力强 / 鼓轮经典结构 / 大水面取向</v>
       </c>
     </row>
     <row r="35">
@@ -2429,19 +2429,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H35" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I35" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%207000%20C%20Round_main.jpg</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K35" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L35" t="str">
-        <v/>
+        <v>经典鼓轮主力</v>
       </c>
       <c r="M35" t="str">
         <v>As big on performance as they are on durability, the Abu Garcia 7000 round reel features a synchronized level wind system that provides even line lay and a smooth retrieve. The updated extended bent handle with power knob gives anglers an edge by increasing torque and aligning the cranking hand closer to the reel for more efficient fighting power. The smooth and consistent multi-disc drag system delivers pressure throughout the entire drag setting. Each 7000 fishing reel is constructed with a corrosion-resistant instant anti-reverse bearing, Duragear™ brass main gear, and a four- pin centrifugal brake for controlled casts.</v>
@@ -2459,10 +2459,10 @@
         <v/>
       </c>
       <c r="R35" t="str">
-        <v/>
+        <v>淡水大物 / 鼓轮泛用</v>
       </c>
       <c r="S35" t="str">
-        <v/>
+        <v>经典鼓轮结构 / 长线容量 / 扭矩稳定</v>
       </c>
     </row>
     <row r="36">
@@ -2488,19 +2488,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H36" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I36" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%207000%20C3%20Round_main.jpg</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K36" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L36" t="str">
-        <v/>
+        <v>经典鼓轮主力</v>
       </c>
       <c r="M36" t="str">
         <v>Big water anglers will appreciate the smooth action of the 2 stainless steel ball bearings + 1 roller bearing in the Ambassadeur® 7000 C3 round reel. This model also offers a corrosion-resistant instant anti-reverse bearing for durability and solid hook setting power. The updated extended bend handle with power knob give anglers an edge by increasing torque and aligning the cranking hand closer to the reel for more efficient fighting power. The Ambassadeur® 7000 C3 fishing reel is equipped with a four-pin centrifugal brake for controlled casts and a one-of-a-kind Carbon Matrix™ drag system that delivers smooth and consistent drag pressure across the entire drag range.</v>
@@ -2518,10 +2518,10 @@
         <v/>
       </c>
       <c r="R36" t="str">
-        <v/>
+        <v>淡水大物 / 鼓轮泛用</v>
       </c>
       <c r="S36" t="str">
-        <v/>
+        <v>经典鼓轮结构 / 长线容量 / 扭矩稳定</v>
       </c>
     </row>
     <row r="37">
@@ -2547,19 +2547,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H37" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I37" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20SX%20Round%20Reel_main.jpg</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K37" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L37" t="str">
-        <v/>
+        <v>经典鼓轮主力</v>
       </c>
       <c r="M37" t="str">
         <v>Power, reliability, and value. The Ambassadeur® SX round reel features a powerful multi-disk drag system that yields up to 12.5 pounds of drag pressure. A recessed reel foot keeps this round baitcast reel low on the rod, making it easy to palm and cast. The addition of a compact bent handle and drag star deliver an ergonomic feel for all day fishing without fatigue. Both the 5600 size and 6600 are available in left and right hand models.</v>
@@ -2577,10 +2577,10 @@
         <v/>
       </c>
       <c r="R37" t="str">
-        <v/>
+        <v>淡水大物 / 鼓轮泛用</v>
       </c>
       <c r="S37" t="str">
-        <v/>
+        <v>经典鼓轮结构 / 长线容量 / 扭矩稳定</v>
       </c>
     </row>
     <row r="38">
@@ -2606,19 +2606,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H38" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I38" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20STX%20Round%20Reel_main.jpg</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K38" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L38" t="str">
-        <v/>
+        <v>经典鼓轮主力</v>
       </c>
       <c r="M38" t="str">
         <v>The Ambassadeur STX round reel delivers the ultimate combination of value and smooth performance in a durable package. Engineered with a 4 + 1 stainless steel bearing system, powerful multi-disk drag, and a compact, bent handle and star, the Ambassadeur STX fits the bill for a variety of species and techniques. The recessed reel foot allows the reel to sit low on the rod, making it easier to palm and cast. Available in left and right hand models, the STX includes a 5600 size model that holds 230 yards of 14lb test mono and a 6600 size that holds 255 yards of 14lb test mono.</v>
@@ -2636,10 +2636,10 @@
         <v/>
       </c>
       <c r="R38" t="str">
-        <v/>
+        <v>淡水大物 / 鼓轮泛用</v>
       </c>
       <c r="S38" t="str">
-        <v/>
+        <v>经典鼓轮结构 / 长线容量 / 扭矩稳定</v>
       </c>
     </row>
     <row r="39">
@@ -2665,19 +2665,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H39" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I39" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20S%20Round%20Reel_main.jpg</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K39" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L39" t="str">
-        <v/>
+        <v>经典鼓轮主力</v>
       </c>
       <c r="M39" t="str">
         <v>Value-packed with power and performance, the Ambassadeur S round baitcast reel gets the job done day after day. Featuring 2 stainless steel ball bearings for smooth operation, 12.5 pounds of drag pressure, and a 4-pin centrifugal brake, this reel delivers power and controlled casting for a variety of situations. The addition of a bent handle and drag star translates into a more ergonomic feel for all day comfort. Both the 5500 and 6500 sizes are available in left and right hand models.</v>
@@ -2695,10 +2695,10 @@
         <v/>
       </c>
       <c r="R39" t="str">
-        <v/>
+        <v>淡水大物 / 鼓轮泛用</v>
       </c>
       <c r="S39" t="str">
-        <v/>
+        <v>经典鼓轮结构 / 长线容量 / 扭矩稳定</v>
       </c>
     </row>
     <row r="40">
@@ -2724,19 +2724,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H40" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I40" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20C4%20Round%20Reel_main.jpg</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K40" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L40" t="str">
-        <v/>
+        <v>经典鼓轮主力</v>
       </c>
       <c r="M40" t="str">
         <v>The tradition continues. With silky-smooth operation and power to spare, the new line of C4 round reels embodies trusted durability and engineering that generations of anglers have come to expect.</v>
@@ -2754,10 +2754,10 @@
         <v/>
       </c>
       <c r="R40" t="str">
-        <v/>
+        <v>淡水大物 / 鼓轮泛用</v>
       </c>
       <c r="S40" t="str">
-        <v/>
+        <v>经典鼓轮结构 / 长线容量 / 扭矩稳定</v>
       </c>
     </row>
     <row r="41">
@@ -2783,19 +2783,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H41" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I41" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20C3%20Round%20Reel_main.jpg</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K41" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L41" t="str">
-        <v/>
+        <v>经典鼓轮主力</v>
       </c>
       <c r="M41" t="str">
         <v>Brute strength meets refined style in this round baitcast reel. Upgraded performance and styling merge with proven strength and engineering. The heritage continues with the new C3 fishing reel, designed to meet the demands of the most hardcore angler.</v>
@@ -2813,10 +2813,10 @@
         <v/>
       </c>
       <c r="R41" t="str">
-        <v/>
+        <v>淡水大物 / 鼓轮泛用</v>
       </c>
       <c r="S41" t="str">
-        <v/>
+        <v>经典鼓轮结构 / 长线容量 / 扭矩稳定</v>
       </c>
     </row>
     <row r="42">
@@ -2842,19 +2842,19 @@
         <v>Round Baitcast Reels</v>
       </c>
       <c r="H42" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="I42" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ambassadeur%C2%AE%20Line%20Counter_main.jpg</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="K42" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="L42" t="str">
-        <v/>
+        <v>经典计数器主力</v>
       </c>
       <c r="M42" t="str">
         <v>The palm-able Line Counter fishing reel features our synchronized levelwind system as well as the smooth-pulling Carbon Matrix™ drag system. Each reel is constructed with three shielded stainless steel ball bearings and a corrosion- resistant instant anti-reverse bearing for solid hook sets. The mechanical line counter measures line in feet as it pulls out for extreme trolling and/or downrigging accuracy.</v>
@@ -2872,10 +2872,10 @@
         <v/>
       </c>
       <c r="R42" t="str">
-        <v/>
+        <v>拖钓 / 深水 / 船钓</v>
       </c>
       <c r="S42" t="str">
-        <v/>
+        <v>机械或数字计数 / 稳定大物取向 / 船钓友好</v>
       </c>
     </row>
   </sheetData>
@@ -2887,7 +2887,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO94"/>
+  <dimension ref="A1:AP94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3013,6 +3013,9 @@
       <c r="AO1" t="str">
         <v>type</v>
       </c>
+      <c r="AP1" t="str">
+        <v>body_material_tech</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -3037,13 +3040,13 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>185/6 / 130/8 / 110/10</v>
+        <v>6/185 / 8/130 / 10/110</v>
       </c>
       <c r="I2" t="str">
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>190/8</v>
+        <v>8/190</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -3061,10 +3064,10 @@
         <v>36282986602</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -3082,10 +3085,10 @@
         <v/>
       </c>
       <c r="W2" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X2" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y2" t="str">
         <v/>
@@ -3097,7 +3100,7 @@
         <v/>
       </c>
       <c r="AB2" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC2" t="str">
         <v/>
@@ -3121,22 +3124,25 @@
         <v/>
       </c>
       <c r="AJ2" t="str">
-        <v/>
+        <v>入门,泛用,岸钓</v>
       </c>
       <c r="AK2" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL2" t="str">
         <v/>
       </c>
       <c r="AM2" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN2" t="str">
         <v/>
       </c>
       <c r="AO2" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP2" t="str">
+        <v>Graphite body and sideplates / MagTrax</v>
       </c>
     </row>
     <row r="3">
@@ -3162,13 +3168,13 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -3186,10 +3192,10 @@
         <v>36282061538</v>
       </c>
       <c r="P3" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q3" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -3207,10 +3213,10 @@
         <v/>
       </c>
       <c r="W3" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X3" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y3" t="str">
         <v/>
@@ -3222,7 +3228,7 @@
         <v/>
       </c>
       <c r="AB3" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC3" t="str">
         <v/>
@@ -3246,22 +3252,25 @@
         <v/>
       </c>
       <c r="AJ3" t="str">
-        <v/>
+        <v>翻转,重障碍,cover</v>
       </c>
       <c r="AK3" t="str">
-        <v/>
+        <v>约 10g+</v>
       </c>
       <c r="AL3" t="str">
         <v/>
       </c>
       <c r="AM3" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN3" t="str">
         <v/>
       </c>
       <c r="AO3" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP3" t="str">
+        <v>A-Sym body / MagTrax / flipping switch</v>
       </c>
     </row>
     <row r="4">
@@ -3287,13 +3296,13 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -3311,10 +3320,10 @@
         <v>36282061545</v>
       </c>
       <c r="P4" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q4" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R4" t="str">
         <v/>
@@ -3332,10 +3341,10 @@
         <v/>
       </c>
       <c r="W4" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X4" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y4" t="str">
         <v/>
@@ -3347,7 +3356,7 @@
         <v/>
       </c>
       <c r="AB4" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC4" t="str">
         <v/>
@@ -3371,22 +3380,25 @@
         <v/>
       </c>
       <c r="AJ4" t="str">
-        <v/>
+        <v>翻转,重障碍,cover</v>
       </c>
       <c r="AK4" t="str">
-        <v/>
+        <v>约 10g+</v>
       </c>
       <c r="AL4" t="str">
         <v/>
       </c>
       <c r="AM4" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN4" t="str">
         <v/>
       </c>
       <c r="AO4" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP4" t="str">
+        <v>A-Sym body / MagTrax / flipping switch</v>
       </c>
     </row>
     <row r="5">
@@ -3412,13 +3424,13 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -3436,10 +3448,10 @@
         <v>36282037625</v>
       </c>
       <c r="P5" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q5" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -3457,10 +3469,10 @@
         <v/>
       </c>
       <c r="W5" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X5" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y5" t="str">
         <v/>
@@ -3472,7 +3484,7 @@
         <v/>
       </c>
       <c r="AB5" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC5" t="str">
         <v/>
@@ -3496,22 +3508,25 @@
         <v/>
       </c>
       <c r="AJ5" t="str">
-        <v/>
+        <v>泛用,入门进阶,鲈鱼</v>
       </c>
       <c r="AK5" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL5" t="str">
         <v/>
       </c>
       <c r="AM5" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN5" t="str">
         <v/>
       </c>
       <c r="AO5" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP5" t="str">
+        <v>A-Sym body / MagTrax</v>
       </c>
     </row>
     <row r="6">
@@ -3537,13 +3552,13 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -3561,10 +3576,10 @@
         <v>36282037649</v>
       </c>
       <c r="P6" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q6" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R6" t="str">
         <v/>
@@ -3582,10 +3597,10 @@
         <v/>
       </c>
       <c r="W6" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X6" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y6" t="str">
         <v/>
@@ -3597,7 +3612,7 @@
         <v/>
       </c>
       <c r="AB6" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC6" t="str">
         <v/>
@@ -3621,22 +3636,25 @@
         <v/>
       </c>
       <c r="AJ6" t="str">
-        <v/>
+        <v>泛用,入门进阶,鲈鱼</v>
       </c>
       <c r="AK6" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL6" t="str">
         <v/>
       </c>
       <c r="AM6" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN6" t="str">
         <v/>
       </c>
       <c r="AO6" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP6" t="str">
+        <v>A-Sym body / MagTrax</v>
       </c>
     </row>
     <row r="7">
@@ -3662,13 +3680,13 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -3686,10 +3704,10 @@
         <v>36282037663</v>
       </c>
       <c r="P7" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R7" t="str">
         <v/>
@@ -3707,10 +3725,10 @@
         <v/>
       </c>
       <c r="W7" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X7" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y7" t="str">
         <v/>
@@ -3722,7 +3740,7 @@
         <v/>
       </c>
       <c r="AB7" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC7" t="str">
         <v/>
@@ -3734,7 +3752,7 @@
         <v/>
       </c>
       <c r="AF7" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG7" t="str">
         <v/>
@@ -3746,22 +3764,25 @@
         <v/>
       </c>
       <c r="AJ7" t="str">
-        <v/>
+        <v>泛用,进阶,鲈鱼</v>
       </c>
       <c r="AK7" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL7" t="str">
         <v/>
       </c>
       <c r="AM7" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN7" t="str">
         <v/>
       </c>
       <c r="AO7" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP7" t="str">
+        <v>A-Sym body / Carbon Matrix / MagTrax</v>
       </c>
     </row>
     <row r="8">
@@ -3787,13 +3808,13 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -3811,10 +3832,10 @@
         <v>36282037687</v>
       </c>
       <c r="P8" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q8" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R8" t="str">
         <v/>
@@ -3832,10 +3853,10 @@
         <v/>
       </c>
       <c r="W8" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X8" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y8" t="str">
         <v/>
@@ -3847,7 +3868,7 @@
         <v/>
       </c>
       <c r="AB8" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC8" t="str">
         <v/>
@@ -3859,7 +3880,7 @@
         <v/>
       </c>
       <c r="AF8" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG8" t="str">
         <v/>
@@ -3871,22 +3892,25 @@
         <v/>
       </c>
       <c r="AJ8" t="str">
-        <v/>
+        <v>泛用,进阶,鲈鱼</v>
       </c>
       <c r="AK8" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL8" t="str">
         <v/>
       </c>
       <c r="AM8" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN8" t="str">
         <v/>
       </c>
       <c r="AO8" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP8" t="str">
+        <v>A-Sym body / Carbon Matrix / MagTrax</v>
       </c>
     </row>
     <row r="9">
@@ -3912,13 +3936,13 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I9" t="str">
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -3936,10 +3960,10 @@
         <v>36282037700</v>
       </c>
       <c r="P9" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q9" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R9" t="str">
         <v/>
@@ -3957,10 +3981,10 @@
         <v/>
       </c>
       <c r="W9" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X9" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y9" t="str">
         <v/>
@@ -3972,7 +3996,7 @@
         <v/>
       </c>
       <c r="AB9" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC9" t="str">
         <v/>
@@ -3996,22 +4020,25 @@
         <v/>
       </c>
       <c r="AJ9" t="str">
-        <v/>
+        <v>低速,crankbait,moving bait</v>
       </c>
       <c r="AK9" t="str">
-        <v/>
+        <v>约 10g+</v>
       </c>
       <c r="AL9" t="str">
         <v/>
       </c>
       <c r="AM9" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN9" t="str">
         <v/>
       </c>
       <c r="AO9" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP9" t="str">
+        <v>A-Sym body / low gear</v>
       </c>
     </row>
     <row r="10">
@@ -4037,13 +4064,13 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I10" t="str">
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -4061,10 +4088,10 @@
         <v>36282037724</v>
       </c>
       <c r="P10" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q10" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -4082,10 +4109,10 @@
         <v/>
       </c>
       <c r="W10" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X10" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -4097,7 +4124,7 @@
         <v/>
       </c>
       <c r="AB10" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC10" t="str">
         <v/>
@@ -4121,22 +4148,25 @@
         <v/>
       </c>
       <c r="AJ10" t="str">
-        <v/>
+        <v>低速,crankbait,moving bait</v>
       </c>
       <c r="AK10" t="str">
-        <v/>
+        <v>约 10g+</v>
       </c>
       <c r="AL10" t="str">
         <v/>
       </c>
       <c r="AM10" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN10" t="str">
         <v/>
       </c>
       <c r="AO10" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP10" t="str">
+        <v>A-Sym body / low gear</v>
       </c>
     </row>
     <row r="11">
@@ -4162,13 +4192,13 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I11" t="str">
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -4186,10 +4216,10 @@
         <v>36282037748</v>
       </c>
       <c r="P11" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q11" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R11" t="str">
         <v/>
@@ -4207,10 +4237,10 @@
         <v/>
       </c>
       <c r="W11" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X11" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y11" t="str">
         <v/>
@@ -4222,7 +4252,7 @@
         <v/>
       </c>
       <c r="AB11" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC11" t="str">
         <v/>
@@ -4246,22 +4276,25 @@
         <v/>
       </c>
       <c r="AJ11" t="str">
-        <v/>
+        <v>高速,搜索,快收</v>
       </c>
       <c r="AK11" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL11" t="str">
         <v/>
       </c>
       <c r="AM11" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN11" t="str">
         <v/>
       </c>
       <c r="AO11" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP11" t="str">
+        <v>A-Sym body / Carbon Matrix / Rocket</v>
       </c>
     </row>
     <row r="12">
@@ -4287,13 +4320,13 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I12" t="str">
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -4311,10 +4344,10 @@
         <v>36282037762</v>
       </c>
       <c r="P12" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R12" t="str">
         <v/>
@@ -4332,10 +4365,10 @@
         <v/>
       </c>
       <c r="W12" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X12" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -4347,7 +4380,7 @@
         <v/>
       </c>
       <c r="AB12" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC12" t="str">
         <v/>
@@ -4371,22 +4404,25 @@
         <v/>
       </c>
       <c r="AJ12" t="str">
-        <v/>
+        <v>高速,搜索,快收</v>
       </c>
       <c r="AK12" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL12" t="str">
         <v/>
       </c>
       <c r="AM12" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN12" t="str">
         <v/>
       </c>
       <c r="AO12" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP12" t="str">
+        <v>A-Sym body / Carbon Matrix / Rocket</v>
       </c>
     </row>
     <row r="13">
@@ -4412,13 +4448,13 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>240/12 / 205/14 / 170/17</v>
+        <v>12/240 / 14/205 / 17/170</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>310/20 / 235/30 / 165/50</v>
+        <v>20/310 / 30/235 / 50/165</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -4436,10 +4472,10 @@
         <v>36282037786</v>
       </c>
       <c r="P13" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R13" t="str">
         <v/>
@@ -4457,10 +4493,10 @@
         <v/>
       </c>
       <c r="W13" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X13" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -4472,7 +4508,7 @@
         <v/>
       </c>
       <c r="AB13" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC13" t="str">
         <v/>
@@ -4496,22 +4532,25 @@
         <v/>
       </c>
       <c r="AJ13" t="str">
-        <v/>
+        <v>big bait,大鱼,重载</v>
       </c>
       <c r="AK13" t="str">
-        <v/>
+        <v>约 20g+</v>
       </c>
       <c r="AL13" t="str">
         <v/>
       </c>
       <c r="AM13" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN13" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO13" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP13" t="str">
+        <v>Power Stack Carbon Matrix / MagTrax</v>
       </c>
     </row>
     <row r="14">
@@ -4537,13 +4576,13 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>240/12 / 205/14 / 170/17</v>
+        <v>12/240 / 14/205 / 17/170</v>
       </c>
       <c r="I14" t="str">
         <v/>
       </c>
       <c r="J14" t="str">
-        <v>310/20 / 235/30 / 165/50</v>
+        <v>20/310 / 30/235 / 50/165</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -4561,10 +4600,10 @@
         <v>36282037809</v>
       </c>
       <c r="P14" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R14" t="str">
         <v/>
@@ -4582,10 +4621,10 @@
         <v/>
       </c>
       <c r="W14" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X14" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y14" t="str">
         <v/>
@@ -4597,7 +4636,7 @@
         <v/>
       </c>
       <c r="AB14" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC14" t="str">
         <v/>
@@ -4621,22 +4660,25 @@
         <v/>
       </c>
       <c r="AJ14" t="str">
-        <v/>
+        <v>big bait,大鱼,重载</v>
       </c>
       <c r="AK14" t="str">
-        <v/>
+        <v>约 20g+</v>
       </c>
       <c r="AL14" t="str">
         <v/>
       </c>
       <c r="AM14" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN14" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO14" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP14" t="str">
+        <v>Power Stack Carbon Matrix / MagTrax</v>
       </c>
     </row>
     <row r="15">
@@ -4662,13 +4704,13 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>295/12 / 250/14 / 205/17</v>
+        <v>12/295 / 14/250 / 17/205</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15" t="str">
-        <v>380/20 / 285/30 / 200/50</v>
+        <v>20/380 / 30/285 / 50/200</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -4686,10 +4728,10 @@
         <v>36282037823</v>
       </c>
       <c r="P15" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R15" t="str">
         <v/>
@@ -4707,10 +4749,10 @@
         <v/>
       </c>
       <c r="W15" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X15" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y15" t="str">
         <v/>
@@ -4722,7 +4764,7 @@
         <v/>
       </c>
       <c r="AB15" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC15" t="str">
         <v/>
@@ -4746,22 +4788,25 @@
         <v/>
       </c>
       <c r="AJ15" t="str">
-        <v/>
+        <v>big bait,大鱼,重载</v>
       </c>
       <c r="AK15" t="str">
-        <v/>
+        <v>约 20g+</v>
       </c>
       <c r="AL15" t="str">
         <v/>
       </c>
       <c r="AM15" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN15" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO15" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP15" t="str">
+        <v>Power Stack Carbon Matrix / MagTrax</v>
       </c>
     </row>
     <row r="16">
@@ -4787,13 +4832,13 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>295/12 / 250/14 / 205/17</v>
+        <v>12/295 / 14/250 / 17/205</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>380/20 / 285/30 / 200/50</v>
+        <v>20/380 / 30/285 / 50/200</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -4811,10 +4856,10 @@
         <v>36282037830</v>
       </c>
       <c r="P16" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R16" t="str">
         <v/>
@@ -4832,10 +4877,10 @@
         <v/>
       </c>
       <c r="W16" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X16" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y16" t="str">
         <v/>
@@ -4847,7 +4892,7 @@
         <v/>
       </c>
       <c r="AB16" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC16" t="str">
         <v/>
@@ -4871,22 +4916,25 @@
         <v/>
       </c>
       <c r="AJ16" t="str">
-        <v/>
+        <v>big bait,大鱼,重载</v>
       </c>
       <c r="AK16" t="str">
-        <v/>
+        <v>约 20g+</v>
       </c>
       <c r="AL16" t="str">
         <v/>
       </c>
       <c r="AM16" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN16" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO16" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP16" t="str">
+        <v>Power Stack Carbon Matrix / MagTrax</v>
       </c>
     </row>
     <row r="17">
@@ -4912,13 +4960,13 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>240/12 / 205/14 / 170/17</v>
+        <v>12/240 / 14/205 / 17/170</v>
       </c>
       <c r="I17" t="str">
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>310/20 / 235/30 / 165/50</v>
+        <v>20/310 / 30/235 / 50/165</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -4936,10 +4984,10 @@
         <v>36282038134</v>
       </c>
       <c r="P17" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R17" t="str">
         <v/>
@@ -4957,10 +5005,10 @@
         <v/>
       </c>
       <c r="W17" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X17" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y17" t="str">
         <v/>
@@ -4972,7 +5020,7 @@
         <v/>
       </c>
       <c r="AB17" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC17" t="str">
         <v/>
@@ -4984,7 +5032,7 @@
         <v/>
       </c>
       <c r="AF17" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG17" t="str">
         <v/>
@@ -4996,22 +5044,25 @@
         <v/>
       </c>
       <c r="AJ17" t="str">
-        <v/>
+        <v>A-rig,swimbait,big bait,大型鱼</v>
       </c>
       <c r="AK17" t="str">
-        <v/>
+        <v>约 28g+</v>
       </c>
       <c r="AL17" t="str">
         <v/>
       </c>
       <c r="AM17" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN17" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO17" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP17" t="str">
+        <v>A-Symmetric body / Power Stack Carbon Matrix / Infini brake</v>
       </c>
     </row>
     <row r="18">
@@ -5037,13 +5088,13 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>240/12 / 205/14 / 170/17</v>
+        <v>12/240 / 14/205 / 17/170</v>
       </c>
       <c r="I18" t="str">
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>310/20 / 235/30 / 165/50</v>
+        <v>20/310 / 30/235 / 50/165</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -5061,10 +5112,10 @@
         <v>36282038141</v>
       </c>
       <c r="P18" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q18" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R18" t="str">
         <v/>
@@ -5082,10 +5133,10 @@
         <v/>
       </c>
       <c r="W18" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X18" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y18" t="str">
         <v/>
@@ -5097,7 +5148,7 @@
         <v/>
       </c>
       <c r="AB18" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC18" t="str">
         <v/>
@@ -5109,7 +5160,7 @@
         <v/>
       </c>
       <c r="AF18" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG18" t="str">
         <v/>
@@ -5121,22 +5172,25 @@
         <v/>
       </c>
       <c r="AJ18" t="str">
-        <v/>
+        <v>A-rig,swimbait,big bait,大型鱼</v>
       </c>
       <c r="AK18" t="str">
-        <v/>
+        <v>约 28g+</v>
       </c>
       <c r="AL18" t="str">
         <v/>
       </c>
       <c r="AM18" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN18" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO18" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP18" t="str">
+        <v>A-Symmetric body / Power Stack Carbon Matrix / Infini brake</v>
       </c>
     </row>
     <row r="19">
@@ -5162,13 +5216,13 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>240/12 / 205/14 / 170/17</v>
+        <v>12/240 / 14/205 / 17/170</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>310/20 / 235/30 / 165/50</v>
+        <v>20/310 / 30/235 / 50/165</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -5186,10 +5240,10 @@
         <v>36282038165</v>
       </c>
       <c r="P19" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q19" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R19" t="str">
         <v/>
@@ -5207,10 +5261,10 @@
         <v/>
       </c>
       <c r="W19" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X19" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y19" t="str">
         <v/>
@@ -5222,7 +5276,7 @@
         <v/>
       </c>
       <c r="AB19" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC19" t="str">
         <v/>
@@ -5234,7 +5288,7 @@
         <v/>
       </c>
       <c r="AF19" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG19" t="str">
         <v/>
@@ -5246,22 +5300,25 @@
         <v/>
       </c>
       <c r="AJ19" t="str">
-        <v/>
+        <v>A-rig,swimbait,big bait,大型鱼</v>
       </c>
       <c r="AK19" t="str">
-        <v/>
+        <v>约 28g+</v>
       </c>
       <c r="AL19" t="str">
         <v/>
       </c>
       <c r="AM19" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN19" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO19" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP19" t="str">
+        <v>A-Symmetric body / Power Stack Carbon Matrix / Infini brake</v>
       </c>
     </row>
     <row r="20">
@@ -5287,13 +5344,13 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>240/12 / 205/14 / 170/17</v>
+        <v>12/240 / 14/205 / 17/170</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>310/20 / 235/30 / 165/50</v>
+        <v>20/310 / 30/235 / 50/165</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -5311,10 +5368,10 @@
         <v>36282038158</v>
       </c>
       <c r="P20" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q20" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R20" t="str">
         <v/>
@@ -5332,10 +5389,10 @@
         <v/>
       </c>
       <c r="W20" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X20" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y20" t="str">
         <v/>
@@ -5347,7 +5404,7 @@
         <v/>
       </c>
       <c r="AB20" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC20" t="str">
         <v/>
@@ -5359,7 +5416,7 @@
         <v/>
       </c>
       <c r="AF20" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG20" t="str">
         <v/>
@@ -5371,22 +5428,25 @@
         <v/>
       </c>
       <c r="AJ20" t="str">
-        <v/>
+        <v>A-rig,swimbait,big bait,大型鱼</v>
       </c>
       <c r="AK20" t="str">
-        <v/>
+        <v>约 28g+</v>
       </c>
       <c r="AL20" t="str">
         <v/>
       </c>
       <c r="AM20" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN20" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO20" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP20" t="str">
+        <v>A-Symmetric body / Power Stack Carbon Matrix / Infini brake</v>
       </c>
     </row>
     <row r="21">
@@ -5412,13 +5472,13 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>220/10 / 180/12 / 130/17</v>
+        <v>10/220 / 12/180 / 17/130</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>235/20 / 175/30 / 125/50</v>
+        <v>20/235 / 30/175 / 50/125</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -5436,10 +5496,10 @@
         <v>36282038110</v>
       </c>
       <c r="P21" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q21" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R21" t="str">
         <v/>
@@ -5457,10 +5517,10 @@
         <v/>
       </c>
       <c r="W21" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X21" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y21" t="str">
         <v/>
@@ -5472,7 +5532,7 @@
         <v/>
       </c>
       <c r="AB21" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC21" t="str">
         <v/>
@@ -5496,22 +5556,25 @@
         <v/>
       </c>
       <c r="AJ21" t="str">
-        <v/>
+        <v>swimbait,big bait,heavy duty</v>
       </c>
       <c r="AK21" t="str">
-        <v/>
+        <v>约 20g+</v>
       </c>
       <c r="AL21" t="str">
         <v/>
       </c>
       <c r="AM21" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN21" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO21" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP21" t="str">
+        <v>A-Symmetric body / Power Stack Carbon Matrix / IVCB-6</v>
       </c>
     </row>
     <row r="22">
@@ -5537,13 +5600,13 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>220/10 / 180/12 / 130/17</v>
+        <v>10/220 / 12/180 / 17/130</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>235/20 / 175/30 / 125/50</v>
+        <v>20/235 / 30/175 / 50/125</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -5561,10 +5624,10 @@
         <v>36282038127</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q22" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R22" t="str">
         <v/>
@@ -5582,10 +5645,10 @@
         <v/>
       </c>
       <c r="W22" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X22" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y22" t="str">
         <v/>
@@ -5597,7 +5660,7 @@
         <v/>
       </c>
       <c r="AB22" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC22" t="str">
         <v/>
@@ -5621,22 +5684,25 @@
         <v/>
       </c>
       <c r="AJ22" t="str">
-        <v/>
+        <v>swimbait,big bait,heavy duty</v>
       </c>
       <c r="AK22" t="str">
-        <v/>
+        <v>约 20g+</v>
       </c>
       <c r="AL22" t="str">
         <v/>
       </c>
       <c r="AM22" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN22" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO22" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP22" t="str">
+        <v>A-Symmetric body / Power Stack Carbon Matrix / IVCB-6</v>
       </c>
     </row>
     <row r="23">
@@ -5662,13 +5728,13 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>55/8 / 35/12 / 25/17</v>
+        <v>8/55 / 12/35 / 17/25</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>45/20 / 35/30 / 25/50</v>
+        <v>20/45 / 30/35 / 50/25</v>
       </c>
       <c r="K23" t="str">
         <v/>
@@ -5686,10 +5752,10 @@
         <v>036282017726</v>
       </c>
       <c r="P23" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q23" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R23" t="str">
         <v/>
@@ -5707,7 +5773,7 @@
         <v/>
       </c>
       <c r="W23" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X23" t="str">
         <v/>
@@ -5722,7 +5788,7 @@
         <v/>
       </c>
       <c r="AB23" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC23" t="str">
         <v/>
@@ -5746,22 +5812,25 @@
         <v/>
       </c>
       <c r="AJ23" t="str">
-        <v/>
+        <v>BFS,轻饵,finesse</v>
       </c>
       <c r="AK23" t="str">
-        <v/>
+        <v>约 2g+</v>
       </c>
       <c r="AL23" t="str">
         <v/>
       </c>
       <c r="AM23" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN23" t="str">
         <v/>
       </c>
       <c r="AO23" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP23" t="str">
+        <v>BFS concept spool / BFS MagTrax</v>
       </c>
     </row>
     <row r="24">
@@ -5787,13 +5856,13 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>55/8 / 35/12 / 25/17</v>
+        <v>8/55 / 12/35 / 17/25</v>
       </c>
       <c r="I24" t="str">
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>45/20 / 35/30 / 25/50</v>
+        <v>20/45 / 30/35 / 50/25</v>
       </c>
       <c r="K24" t="str">
         <v/>
@@ -5811,10 +5880,10 @@
         <v>036282017733</v>
       </c>
       <c r="P24" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q24" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R24" t="str">
         <v/>
@@ -5832,7 +5901,7 @@
         <v/>
       </c>
       <c r="W24" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X24" t="str">
         <v/>
@@ -5847,7 +5916,7 @@
         <v/>
       </c>
       <c r="AB24" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC24" t="str">
         <v/>
@@ -5871,22 +5940,25 @@
         <v/>
       </c>
       <c r="AJ24" t="str">
-        <v/>
+        <v>BFS,轻饵,finesse</v>
       </c>
       <c r="AK24" t="str">
-        <v/>
+        <v>约 2g+</v>
       </c>
       <c r="AL24" t="str">
         <v/>
       </c>
       <c r="AM24" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN24" t="str">
         <v/>
       </c>
       <c r="AO24" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP24" t="str">
+        <v>BFS concept spool / BFS MagTrax</v>
       </c>
     </row>
     <row r="25">
@@ -5912,13 +5984,13 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>135/10 / 110/12 / 95/14</v>
+        <v>10/135 / 12/110 / 14/95</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K25" t="str">
         <v/>
@@ -5936,10 +6008,10 @@
         <v>036282010246</v>
       </c>
       <c r="P25" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q25" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R25" t="str">
         <v/>
@@ -5957,7 +6029,7 @@
         <v/>
       </c>
       <c r="W25" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X25" t="str">
         <v/>
@@ -5972,7 +6044,7 @@
         <v/>
       </c>
       <c r="AB25" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC25" t="str">
         <v/>
@@ -5984,7 +6056,7 @@
         <v/>
       </c>
       <c r="AF25" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG25" t="str">
         <v/>
@@ -5996,22 +6068,25 @@
         <v/>
       </c>
       <c r="AJ25" t="str">
-        <v/>
+        <v>竞技,泛用,签名款</v>
       </c>
       <c r="AK25" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL25" t="str">
         <v/>
       </c>
       <c r="AM25" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN25" t="str">
         <v/>
       </c>
       <c r="AO25" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP25" t="str">
+        <v>Carbon Matrix / Infini brake</v>
       </c>
     </row>
     <row r="26">
@@ -6037,13 +6112,13 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>135/10 / 110/12 / 95/14</v>
+        <v>10/135 / 12/110 / 14/95</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K26" t="str">
         <v/>
@@ -6061,10 +6136,10 @@
         <v>036282010253</v>
       </c>
       <c r="P26" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q26" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R26" t="str">
         <v/>
@@ -6082,7 +6157,7 @@
         <v/>
       </c>
       <c r="W26" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X26" t="str">
         <v/>
@@ -6097,7 +6172,7 @@
         <v/>
       </c>
       <c r="AB26" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC26" t="str">
         <v/>
@@ -6109,7 +6184,7 @@
         <v/>
       </c>
       <c r="AF26" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG26" t="str">
         <v/>
@@ -6121,22 +6196,25 @@
         <v/>
       </c>
       <c r="AJ26" t="str">
-        <v/>
+        <v>竞技,泛用,签名款</v>
       </c>
       <c r="AK26" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL26" t="str">
         <v/>
       </c>
       <c r="AM26" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN26" t="str">
         <v/>
       </c>
       <c r="AO26" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP26" t="str">
+        <v>Carbon Matrix / Infini brake</v>
       </c>
     </row>
     <row r="27">
@@ -6162,13 +6240,13 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>135/10 / 110/12 / 95/14</v>
+        <v>10/135 / 12/110 / 14/95</v>
       </c>
       <c r="I27" t="str">
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K27" t="str">
         <v/>
@@ -6186,10 +6264,10 @@
         <v>036282010260</v>
       </c>
       <c r="P27" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q27" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R27" t="str">
         <v/>
@@ -6207,7 +6285,7 @@
         <v/>
       </c>
       <c r="W27" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X27" t="str">
         <v/>
@@ -6222,7 +6300,7 @@
         <v/>
       </c>
       <c r="AB27" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC27" t="str">
         <v/>
@@ -6234,7 +6312,7 @@
         <v/>
       </c>
       <c r="AF27" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG27" t="str">
         <v/>
@@ -6246,22 +6324,25 @@
         <v/>
       </c>
       <c r="AJ27" t="str">
-        <v/>
+        <v>竞技,泛用,签名款</v>
       </c>
       <c r="AK27" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL27" t="str">
         <v/>
       </c>
       <c r="AM27" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN27" t="str">
         <v/>
       </c>
       <c r="AO27" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP27" t="str">
+        <v>Carbon Matrix / Infini brake</v>
       </c>
     </row>
     <row r="28">
@@ -6287,13 +6368,13 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>220/10 / 180/12 / 130/17</v>
+        <v>10/220 / 12/180 / 17/130</v>
       </c>
       <c r="I28" t="str">
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>235/20 / 175/30 / 125/50</v>
+        <v>20/235 / 30/175 / 50/125</v>
       </c>
       <c r="K28" t="str">
         <v/>
@@ -6311,10 +6392,10 @@
         <v>036282005730</v>
       </c>
       <c r="P28" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q28" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R28" t="str">
         <v/>
@@ -6332,7 +6413,7 @@
         <v/>
       </c>
       <c r="W28" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X28" t="str">
         <v/>
@@ -6347,7 +6428,7 @@
         <v/>
       </c>
       <c r="AB28" t="str">
-        <v/>
+        <v>海水路亚</v>
       </c>
       <c r="AC28" t="str">
         <v/>
@@ -6371,22 +6452,25 @@
         <v/>
       </c>
       <c r="AJ28" t="str">
-        <v/>
+        <v>近海,咸淡水,海鲈</v>
       </c>
       <c r="AK28" t="str">
-        <v/>
+        <v>约 10g+</v>
       </c>
       <c r="AL28" t="str">
         <v/>
       </c>
       <c r="AM28" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN28" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO28" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP28" t="str">
+        <v>HPCR / D2 Gear Design / saltwater corrosion protection</v>
       </c>
     </row>
     <row r="29">
@@ -6412,13 +6496,13 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>65/6 / 50/8 / 40/10</v>
+        <v>6/65 / 8/50 / 10/40</v>
       </c>
       <c r="I29" t="str">
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>100/6 / 80/8 / 70/10</v>
+        <v>6/100 / 8/80 / 10/70</v>
       </c>
       <c r="K29" t="str">
         <v/>
@@ -6436,10 +6520,10 @@
         <v>36282121553</v>
       </c>
       <c r="P29" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q29" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R29" t="str">
         <v/>
@@ -6457,10 +6541,10 @@
         <v/>
       </c>
       <c r="W29" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X29" t="str">
-        <v/>
+        <v>航空级铝</v>
       </c>
       <c r="Y29" t="str">
         <v/>
@@ -6472,7 +6556,7 @@
         <v/>
       </c>
       <c r="AB29" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC29" t="str">
         <v/>
@@ -6496,22 +6580,25 @@
         <v/>
       </c>
       <c r="AJ29" t="str">
-        <v/>
+        <v>BFS,轻饵,finesse</v>
       </c>
       <c r="AK29" t="str">
-        <v/>
+        <v>约 1g+</v>
       </c>
       <c r="AL29" t="str">
         <v/>
       </c>
       <c r="AM29" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN29" t="str">
         <v/>
       </c>
       <c r="AO29" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP29" t="str">
+        <v>BFS concept spool / MagTrax BFS / CeramiLite</v>
       </c>
     </row>
     <row r="30">
@@ -6537,13 +6624,13 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>65/6 / 50/8 / 40/10</v>
+        <v>6/65 / 8/50 / 10/40</v>
       </c>
       <c r="I30" t="str">
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>100/6 / 80/8 / 70/10</v>
+        <v>6/100 / 8/80 / 10/70</v>
       </c>
       <c r="K30" t="str">
         <v/>
@@ -6561,10 +6648,10 @@
         <v>36282121560</v>
       </c>
       <c r="P30" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q30" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R30" t="str">
         <v/>
@@ -6582,10 +6669,10 @@
         <v/>
       </c>
       <c r="W30" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X30" t="str">
-        <v/>
+        <v>航空级铝</v>
       </c>
       <c r="Y30" t="str">
         <v/>
@@ -6597,7 +6684,7 @@
         <v/>
       </c>
       <c r="AB30" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC30" t="str">
         <v/>
@@ -6621,22 +6708,25 @@
         <v/>
       </c>
       <c r="AJ30" t="str">
-        <v/>
+        <v>BFS,轻饵,finesse</v>
       </c>
       <c r="AK30" t="str">
-        <v/>
+        <v>约 1g+</v>
       </c>
       <c r="AL30" t="str">
         <v/>
       </c>
       <c r="AM30" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN30" t="str">
         <v/>
       </c>
       <c r="AO30" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP30" t="str">
+        <v>BFS concept spool / MagTrax BFS / CeramiLite</v>
       </c>
     </row>
     <row r="31">
@@ -6662,13 +6752,13 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>65/6 / 50/8 / 40/10</v>
+        <v>6/65 / 8/50 / 10/40</v>
       </c>
       <c r="I31" t="str">
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>100/6 / 80/8 / 70/10</v>
+        <v>6/100 / 8/80 / 10/70</v>
       </c>
       <c r="K31" t="str">
         <v/>
@@ -6686,10 +6776,10 @@
         <v>36282121997</v>
       </c>
       <c r="P31" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q31" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R31" t="str">
         <v/>
@@ -6707,10 +6797,10 @@
         <v/>
       </c>
       <c r="W31" t="str">
-        <v/>
+        <v>X2-Cräftic 铝</v>
       </c>
       <c r="X31" t="str">
-        <v/>
+        <v>航空级铝</v>
       </c>
       <c r="Y31" t="str">
         <v/>
@@ -6722,7 +6812,7 @@
         <v/>
       </c>
       <c r="AB31" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC31" t="str">
         <v/>
@@ -6746,22 +6836,25 @@
         <v/>
       </c>
       <c r="AJ31" t="str">
-        <v/>
+        <v>BFS,轻饵,finesse</v>
       </c>
       <c r="AK31" t="str">
-        <v/>
+        <v>约 1g+</v>
       </c>
       <c r="AL31" t="str">
         <v/>
       </c>
       <c r="AM31" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN31" t="str">
         <v/>
       </c>
       <c r="AO31" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP31" t="str">
+        <v>BFS concept spool / MagTrax BFS / CeramiLite</v>
       </c>
     </row>
     <row r="32">
@@ -6787,13 +6880,13 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>70/10 / 55/12 / 40/17</v>
+        <v>10/70 / 12/55 / 17/40</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>75/20 / 55/30 / 40/50</v>
+        <v>20/75 / 30/55 / 50/40</v>
       </c>
       <c r="K32" t="str">
         <v/>
@@ -6811,10 +6904,10 @@
         <v>036282731332</v>
       </c>
       <c r="P32" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q32" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R32" t="str">
         <v/>
@@ -6832,7 +6925,7 @@
         <v/>
       </c>
       <c r="W32" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X32" t="str">
         <v/>
@@ -6847,7 +6940,7 @@
         <v/>
       </c>
       <c r="AB32" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC32" t="str">
         <v/>
@@ -6871,22 +6964,25 @@
         <v/>
       </c>
       <c r="AJ32" t="str">
-        <v/>
+        <v>skipping,pitching,flipping,cover</v>
       </c>
       <c r="AK32" t="str">
-        <v/>
+        <v>约 5g+</v>
       </c>
       <c r="AL32" t="str">
         <v/>
       </c>
       <c r="AM32" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN32" t="str">
         <v/>
       </c>
       <c r="AO32" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP32" t="str">
+        <v>EXD / IVCB-6 / shallow spool</v>
       </c>
     </row>
     <row r="33">
@@ -6912,13 +7008,13 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>70/10 / 55/12 / 40/17</v>
+        <v>10/70 / 12/55 / 17/40</v>
       </c>
       <c r="I33" t="str">
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>75/20 / 55/30 / 40/50</v>
+        <v>20/75 / 30/55 / 50/40</v>
       </c>
       <c r="K33" t="str">
         <v/>
@@ -6936,10 +7032,10 @@
         <v>036282731349</v>
       </c>
       <c r="P33" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q33" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R33" t="str">
         <v/>
@@ -6957,7 +7053,7 @@
         <v/>
       </c>
       <c r="W33" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X33" t="str">
         <v/>
@@ -6972,7 +7068,7 @@
         <v/>
       </c>
       <c r="AB33" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC33" t="str">
         <v/>
@@ -6996,22 +7092,25 @@
         <v/>
       </c>
       <c r="AJ33" t="str">
-        <v/>
+        <v>skipping,pitching,flipping,cover</v>
       </c>
       <c r="AK33" t="str">
-        <v/>
+        <v>约 5g+</v>
       </c>
       <c r="AL33" t="str">
         <v/>
       </c>
       <c r="AM33" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN33" t="str">
         <v/>
       </c>
       <c r="AO33" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP33" t="str">
+        <v>EXD / IVCB-6 / shallow spool</v>
       </c>
     </row>
     <row r="34">
@@ -7037,13 +7136,13 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>135/10 / 110/12 / 80/17</v>
+        <v>10/135 / 12/110 / 17/80</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K34" t="str">
         <v/>
@@ -7061,10 +7160,10 @@
         <v>036282106161</v>
       </c>
       <c r="P34" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q34" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R34" t="str">
         <v/>
@@ -7082,7 +7181,7 @@
         <v/>
       </c>
       <c r="W34" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X34" t="str">
         <v/>
@@ -7097,7 +7196,7 @@
         <v/>
       </c>
       <c r="AB34" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC34" t="str">
         <v/>
@@ -7121,22 +7220,25 @@
         <v/>
       </c>
       <c r="AJ34" t="str">
-        <v/>
+        <v>全能,鲈鱼,泛用</v>
       </c>
       <c r="AK34" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL34" t="str">
         <v/>
       </c>
       <c r="AM34" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN34" t="str">
         <v/>
       </c>
       <c r="AO34" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP34" t="str">
+        <v>EXD / MagTrax / Carbon Matrix</v>
       </c>
     </row>
     <row r="35">
@@ -7162,13 +7264,13 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>135/10 / 110/12 / 80/17</v>
+        <v>10/135 / 12/110 / 17/80</v>
       </c>
       <c r="I35" t="str">
         <v/>
       </c>
       <c r="J35" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K35" t="str">
         <v/>
@@ -7186,10 +7288,10 @@
         <v>036282106147</v>
       </c>
       <c r="P35" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q35" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R35" t="str">
         <v/>
@@ -7207,7 +7309,7 @@
         <v/>
       </c>
       <c r="W35" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X35" t="str">
         <v/>
@@ -7222,7 +7324,7 @@
         <v/>
       </c>
       <c r="AB35" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC35" t="str">
         <v/>
@@ -7246,22 +7348,25 @@
         <v/>
       </c>
       <c r="AJ35" t="str">
-        <v/>
+        <v>全能,鲈鱼,泛用</v>
       </c>
       <c r="AK35" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL35" t="str">
         <v/>
       </c>
       <c r="AM35" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN35" t="str">
         <v/>
       </c>
       <c r="AO35" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP35" t="str">
+        <v>EXD / MagTrax / Carbon Matrix</v>
       </c>
     </row>
     <row r="36">
@@ -7287,13 +7392,13 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>135/10 / 110/12 / 80/17</v>
+        <v>10/135 / 12/110 / 17/80</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K36" t="str">
         <v/>
@@ -7311,10 +7416,10 @@
         <v>036282106185</v>
       </c>
       <c r="P36" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q36" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R36" t="str">
         <v/>
@@ -7332,7 +7437,7 @@
         <v/>
       </c>
       <c r="W36" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X36" t="str">
         <v/>
@@ -7347,7 +7452,7 @@
         <v/>
       </c>
       <c r="AB36" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC36" t="str">
         <v/>
@@ -7371,22 +7476,25 @@
         <v/>
       </c>
       <c r="AJ36" t="str">
-        <v/>
+        <v>全能,鲈鱼,泛用</v>
       </c>
       <c r="AK36" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL36" t="str">
         <v/>
       </c>
       <c r="AM36" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN36" t="str">
         <v/>
       </c>
       <c r="AO36" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP36" t="str">
+        <v>EXD / MagTrax / Carbon Matrix</v>
       </c>
     </row>
     <row r="37">
@@ -7412,13 +7520,13 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>135/10 / 110/12 / 80/17</v>
+        <v>10/135 / 12/110 / 17/80</v>
       </c>
       <c r="I37" t="str">
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K37" t="str">
         <v/>
@@ -7436,10 +7544,10 @@
         <v>036282106178</v>
       </c>
       <c r="P37" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q37" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R37" t="str">
         <v/>
@@ -7457,7 +7565,7 @@
         <v/>
       </c>
       <c r="W37" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X37" t="str">
         <v/>
@@ -7472,7 +7580,7 @@
         <v/>
       </c>
       <c r="AB37" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC37" t="str">
         <v/>
@@ -7496,22 +7604,25 @@
         <v/>
       </c>
       <c r="AJ37" t="str">
-        <v/>
+        <v>全能,鲈鱼,泛用</v>
       </c>
       <c r="AK37" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL37" t="str">
         <v/>
       </c>
       <c r="AM37" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN37" t="str">
         <v/>
       </c>
       <c r="AO37" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP37" t="str">
+        <v>EXD / MagTrax / Carbon Matrix</v>
       </c>
     </row>
     <row r="38">
@@ -7537,13 +7648,13 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>135/10 / 110/12 / 80/17</v>
+        <v>10/135 / 12/110 / 17/80</v>
       </c>
       <c r="I38" t="str">
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K38" t="str">
         <v/>
@@ -7561,10 +7672,10 @@
         <v>036282106154</v>
       </c>
       <c r="P38" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q38" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R38" t="str">
         <v/>
@@ -7582,7 +7693,7 @@
         <v/>
       </c>
       <c r="W38" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X38" t="str">
         <v/>
@@ -7597,7 +7708,7 @@
         <v/>
       </c>
       <c r="AB38" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC38" t="str">
         <v/>
@@ -7621,22 +7732,25 @@
         <v/>
       </c>
       <c r="AJ38" t="str">
-        <v/>
+        <v>全能,鲈鱼,泛用</v>
       </c>
       <c r="AK38" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL38" t="str">
         <v/>
       </c>
       <c r="AM38" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN38" t="str">
         <v/>
       </c>
       <c r="AO38" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP38" t="str">
+        <v>EXD / MagTrax / Carbon Matrix</v>
       </c>
     </row>
     <row r="39">
@@ -7662,13 +7776,13 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>135/10 / 110/12 / 80/17</v>
+        <v>10/135 / 12/110 / 17/80</v>
       </c>
       <c r="I39" t="str">
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K39" t="str">
         <v/>
@@ -7686,10 +7800,10 @@
         <v>036282106192</v>
       </c>
       <c r="P39" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q39" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R39" t="str">
         <v/>
@@ -7707,7 +7821,7 @@
         <v/>
       </c>
       <c r="W39" t="str">
-        <v/>
+        <v>C6 碳</v>
       </c>
       <c r="X39" t="str">
         <v/>
@@ -7722,7 +7836,7 @@
         <v/>
       </c>
       <c r="AB39" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC39" t="str">
         <v/>
@@ -7746,22 +7860,25 @@
         <v/>
       </c>
       <c r="AJ39" t="str">
-        <v/>
+        <v>全能,鲈鱼,泛用</v>
       </c>
       <c r="AK39" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL39" t="str">
         <v/>
       </c>
       <c r="AM39" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN39" t="str">
         <v/>
       </c>
       <c r="AO39" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP39" t="str">
+        <v>EXD / MagTrax / Carbon Matrix</v>
       </c>
     </row>
     <row r="40">
@@ -7787,13 +7904,13 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I40" t="str">
         <v/>
       </c>
       <c r="J40" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K40" t="str">
         <v/>
@@ -7811,10 +7928,10 @@
         <v>036282106208</v>
       </c>
       <c r="P40" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q40" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R40" t="str">
         <v/>
@@ -7832,7 +7949,7 @@
         <v/>
       </c>
       <c r="W40" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X40" t="str">
         <v/>
@@ -7847,7 +7964,7 @@
         <v/>
       </c>
       <c r="AB40" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC40" t="str">
         <v/>
@@ -7871,22 +7988,25 @@
         <v/>
       </c>
       <c r="AJ40" t="str">
-        <v/>
+        <v>workhorse,全能,鲈鱼</v>
       </c>
       <c r="AK40" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL40" t="str">
         <v/>
       </c>
       <c r="AM40" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN40" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO40" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP40" t="str">
+        <v>EXD / IVCB-6 / Power Stack Carbon Matrix</v>
       </c>
     </row>
     <row r="41">
@@ -7912,13 +8032,13 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I41" t="str">
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K41" t="str">
         <v/>
@@ -7936,10 +8056,10 @@
         <v>036282106215</v>
       </c>
       <c r="P41" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q41" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R41" t="str">
         <v/>
@@ -7957,7 +8077,7 @@
         <v/>
       </c>
       <c r="W41" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X41" t="str">
         <v/>
@@ -7972,7 +8092,7 @@
         <v/>
       </c>
       <c r="AB41" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC41" t="str">
         <v/>
@@ -7996,22 +8116,25 @@
         <v/>
       </c>
       <c r="AJ41" t="str">
-        <v/>
+        <v>workhorse,全能,鲈鱼</v>
       </c>
       <c r="AK41" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL41" t="str">
         <v/>
       </c>
       <c r="AM41" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN41" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO41" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP41" t="str">
+        <v>EXD / IVCB-6 / Power Stack Carbon Matrix</v>
       </c>
     </row>
     <row r="42">
@@ -8037,13 +8160,13 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I42" t="str">
         <v/>
       </c>
       <c r="J42" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K42" t="str">
         <v/>
@@ -8061,10 +8184,10 @@
         <v>036282106222</v>
       </c>
       <c r="P42" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q42" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R42" t="str">
         <v/>
@@ -8082,7 +8205,7 @@
         <v/>
       </c>
       <c r="W42" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X42" t="str">
         <v/>
@@ -8097,7 +8220,7 @@
         <v/>
       </c>
       <c r="AB42" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC42" t="str">
         <v/>
@@ -8121,22 +8244,25 @@
         <v/>
       </c>
       <c r="AJ42" t="str">
-        <v/>
+        <v>workhorse,全能,鲈鱼</v>
       </c>
       <c r="AK42" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL42" t="str">
         <v/>
       </c>
       <c r="AM42" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN42" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO42" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP42" t="str">
+        <v>EXD / IVCB-6 / Power Stack Carbon Matrix</v>
       </c>
     </row>
     <row r="43">
@@ -8162,13 +8288,13 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I43" t="str">
         <v/>
       </c>
       <c r="J43" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K43" t="str">
         <v/>
@@ -8186,10 +8312,10 @@
         <v>036282106239</v>
       </c>
       <c r="P43" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q43" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R43" t="str">
         <v/>
@@ -8207,7 +8333,7 @@
         <v/>
       </c>
       <c r="W43" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X43" t="str">
         <v/>
@@ -8222,7 +8348,7 @@
         <v/>
       </c>
       <c r="AB43" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC43" t="str">
         <v/>
@@ -8246,22 +8372,25 @@
         <v/>
       </c>
       <c r="AJ43" t="str">
-        <v/>
+        <v>workhorse,全能,鲈鱼</v>
       </c>
       <c r="AK43" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL43" t="str">
         <v/>
       </c>
       <c r="AM43" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN43" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO43" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP43" t="str">
+        <v>EXD / IVCB-6 / Power Stack Carbon Matrix</v>
       </c>
     </row>
     <row r="44">
@@ -8287,13 +8416,13 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I44" t="str">
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K44" t="str">
         <v/>
@@ -8311,10 +8440,10 @@
         <v>036282106307</v>
       </c>
       <c r="P44" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q44" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R44" t="str">
         <v/>
@@ -8332,7 +8461,7 @@
         <v/>
       </c>
       <c r="W44" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X44" t="str">
         <v/>
@@ -8347,7 +8476,7 @@
         <v/>
       </c>
       <c r="AB44" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC44" t="str">
         <v/>
@@ -8371,22 +8500,25 @@
         <v/>
       </c>
       <c r="AJ44" t="str">
-        <v/>
+        <v>高端,全能,竞技</v>
       </c>
       <c r="AK44" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL44" t="str">
         <v/>
       </c>
       <c r="AM44" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN44" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO44" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP44" t="str">
+        <v>EXD / IVCB-6 / Power Stack Carbon Matrix</v>
       </c>
     </row>
     <row r="45">
@@ -8412,13 +8544,13 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I45" t="str">
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K45" t="str">
         <v/>
@@ -8436,10 +8568,10 @@
         <v>036282106314</v>
       </c>
       <c r="P45" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q45" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R45" t="str">
         <v/>
@@ -8457,7 +8589,7 @@
         <v/>
       </c>
       <c r="W45" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X45" t="str">
         <v/>
@@ -8472,7 +8604,7 @@
         <v/>
       </c>
       <c r="AB45" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC45" t="str">
         <v/>
@@ -8496,22 +8628,25 @@
         <v/>
       </c>
       <c r="AJ45" t="str">
-        <v/>
+        <v>高端,全能,竞技</v>
       </c>
       <c r="AK45" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL45" t="str">
         <v/>
       </c>
       <c r="AM45" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN45" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO45" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP45" t="str">
+        <v>EXD / IVCB-6 / Power Stack Carbon Matrix</v>
       </c>
     </row>
     <row r="46">
@@ -8537,13 +8672,13 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I46" t="str">
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K46" t="str">
         <v/>
@@ -8561,10 +8696,10 @@
         <v>036282106321</v>
       </c>
       <c r="P46" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q46" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R46" t="str">
         <v/>
@@ -8582,7 +8717,7 @@
         <v/>
       </c>
       <c r="W46" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X46" t="str">
         <v/>
@@ -8597,7 +8732,7 @@
         <v/>
       </c>
       <c r="AB46" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC46" t="str">
         <v/>
@@ -8621,22 +8756,25 @@
         <v/>
       </c>
       <c r="AJ46" t="str">
-        <v/>
+        <v>高端,全能,竞技</v>
       </c>
       <c r="AK46" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL46" t="str">
         <v/>
       </c>
       <c r="AM46" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN46" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO46" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP46" t="str">
+        <v>EXD / IVCB-6 / Power Stack Carbon Matrix</v>
       </c>
     </row>
     <row r="47">
@@ -8662,13 +8800,13 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I47" t="str">
         <v/>
       </c>
       <c r="J47" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K47" t="str">
         <v/>
@@ -8686,10 +8824,10 @@
         <v>036282106338</v>
       </c>
       <c r="P47" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q47" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R47" t="str">
         <v/>
@@ -8707,7 +8845,7 @@
         <v/>
       </c>
       <c r="W47" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X47" t="str">
         <v/>
@@ -8722,7 +8860,7 @@
         <v/>
       </c>
       <c r="AB47" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC47" t="str">
         <v/>
@@ -8746,22 +8884,25 @@
         <v/>
       </c>
       <c r="AJ47" t="str">
-        <v/>
+        <v>高端,全能,竞技</v>
       </c>
       <c r="AK47" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL47" t="str">
         <v/>
       </c>
       <c r="AM47" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN47" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO47" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP47" t="str">
+        <v>EXD / IVCB-6 / Power Stack Carbon Matrix</v>
       </c>
     </row>
     <row r="48">
@@ -8787,13 +8928,13 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I48" t="str">
         <v/>
       </c>
       <c r="J48" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K48" t="str">
         <v/>
@@ -8811,10 +8952,10 @@
         <v>036282106284</v>
       </c>
       <c r="P48" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q48" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R48" t="str">
         <v/>
@@ -8832,7 +8973,7 @@
         <v/>
       </c>
       <c r="W48" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X48" t="str">
         <v/>
@@ -8847,7 +8988,7 @@
         <v/>
       </c>
       <c r="AB48" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC48" t="str">
         <v/>
@@ -8871,22 +9012,25 @@
         <v/>
       </c>
       <c r="AJ48" t="str">
-        <v/>
+        <v>高速,搜索,快收</v>
       </c>
       <c r="AK48" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL48" t="str">
         <v/>
       </c>
       <c r="AM48" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN48" t="str">
         <v/>
       </c>
       <c r="AO48" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP48" t="str">
+        <v>EXD / IVCB-6 / high gear</v>
       </c>
     </row>
     <row r="49">
@@ -8912,13 +9056,13 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I49" t="str">
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K49" t="str">
         <v/>
@@ -8936,10 +9080,10 @@
         <v>036282106291</v>
       </c>
       <c r="P49" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q49" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R49" t="str">
         <v/>
@@ -8957,7 +9101,7 @@
         <v/>
       </c>
       <c r="W49" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X49" t="str">
         <v/>
@@ -8972,7 +9116,7 @@
         <v/>
       </c>
       <c r="AB49" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC49" t="str">
         <v/>
@@ -8996,22 +9140,25 @@
         <v/>
       </c>
       <c r="AJ49" t="str">
-        <v/>
+        <v>高速,搜索,快收</v>
       </c>
       <c r="AK49" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL49" t="str">
         <v/>
       </c>
       <c r="AM49" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN49" t="str">
         <v/>
       </c>
       <c r="AO49" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP49" t="str">
+        <v>EXD / IVCB-6 / high gear</v>
       </c>
     </row>
     <row r="50">
@@ -9037,13 +9184,13 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I50" t="str">
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K50" t="str">
         <v/>
@@ -9061,10 +9208,10 @@
         <v>036282106246</v>
       </c>
       <c r="P50" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q50" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R50" t="str">
         <v/>
@@ -9082,7 +9229,7 @@
         <v/>
       </c>
       <c r="W50" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X50" t="str">
         <v/>
@@ -9097,7 +9244,7 @@
         <v/>
       </c>
       <c r="AB50" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC50" t="str">
         <v/>
@@ -9121,22 +9268,25 @@
         <v/>
       </c>
       <c r="AJ50" t="str">
-        <v/>
+        <v>高速,搜索,快收</v>
       </c>
       <c r="AK50" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL50" t="str">
         <v/>
       </c>
       <c r="AM50" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN50" t="str">
         <v/>
       </c>
       <c r="AO50" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP50" t="str">
+        <v>EXD / IVCB-6 / high gear</v>
       </c>
     </row>
     <row r="51">
@@ -9162,13 +9312,13 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>160/10 / 130/12 / 90/17</v>
+        <v>10/160 / 12/130 / 17/90</v>
       </c>
       <c r="I51" t="str">
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>170/20 / 125/30 / 90/50</v>
+        <v>20/170 / 30/125 / 50/90</v>
       </c>
       <c r="K51" t="str">
         <v/>
@@ -9186,10 +9336,10 @@
         <v>036282106253</v>
       </c>
       <c r="P51" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q51" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R51" t="str">
         <v/>
@@ -9207,7 +9357,7 @@
         <v/>
       </c>
       <c r="W51" t="str">
-        <v/>
+        <v>X2-Cräftic 合金</v>
       </c>
       <c r="X51" t="str">
         <v/>
@@ -9222,7 +9372,7 @@
         <v/>
       </c>
       <c r="AB51" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC51" t="str">
         <v/>
@@ -9246,22 +9396,25 @@
         <v/>
       </c>
       <c r="AJ51" t="str">
-        <v/>
+        <v>高速,搜索,快收</v>
       </c>
       <c r="AK51" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL51" t="str">
         <v/>
       </c>
       <c r="AM51" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN51" t="str">
         <v/>
       </c>
       <c r="AO51" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP51" t="str">
+        <v>EXD / IVCB-6 / high gear</v>
       </c>
     </row>
     <row r="52">
@@ -9287,13 +9440,13 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>135/10 / 110/12 / 80/17</v>
+        <v>10/135 / 12/110 / 17/80</v>
       </c>
       <c r="I52" t="str">
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>135/20 / 105/30 / 75/50</v>
+        <v>20/135 / 30/105 / 50/75</v>
       </c>
       <c r="K52" t="str">
         <v/>
@@ -9311,10 +9464,10 @@
         <v>036282967724</v>
       </c>
       <c r="P52" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q52" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R52" t="str">
         <v/>
@@ -9335,7 +9488,7 @@
         <v/>
       </c>
       <c r="X52" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y52" t="str">
         <v/>
@@ -9347,7 +9500,7 @@
         <v/>
       </c>
       <c r="AB52" t="str">
-        <v/>
+        <v>船钓 / 拖钓</v>
       </c>
       <c r="AC52" t="str">
         <v/>
@@ -9371,7 +9524,7 @@
         <v/>
       </c>
       <c r="AJ52" t="str">
-        <v/>
+        <v>计数器,船钓,深水</v>
       </c>
       <c r="AK52" t="str">
         <v/>
@@ -9380,13 +9533,16 @@
         <v/>
       </c>
       <c r="AM52" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN52" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO52" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP52" t="str">
+        <v>Digital line counter / DTT warning</v>
       </c>
     </row>
     <row r="53">
@@ -9412,13 +9568,13 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>135/10 / 110/12 / 80/17</v>
+        <v>10/135 / 12/110 / 17/80</v>
       </c>
       <c r="I53" t="str">
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>135/20 / 105/30 / 75/50</v>
+        <v>20/135 / 30/105 / 50/75</v>
       </c>
       <c r="K53" t="str">
         <v/>
@@ -9436,10 +9592,10 @@
         <v>036282967717</v>
       </c>
       <c r="P53" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q53" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R53" t="str">
         <v/>
@@ -9460,7 +9616,7 @@
         <v/>
       </c>
       <c r="X53" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y53" t="str">
         <v/>
@@ -9472,7 +9628,7 @@
         <v/>
       </c>
       <c r="AB53" t="str">
-        <v/>
+        <v>船钓 / 拖钓</v>
       </c>
       <c r="AC53" t="str">
         <v/>
@@ -9496,7 +9652,7 @@
         <v/>
       </c>
       <c r="AJ53" t="str">
-        <v/>
+        <v>计数器,船钓,深水</v>
       </c>
       <c r="AK53" t="str">
         <v/>
@@ -9505,13 +9661,16 @@
         <v/>
       </c>
       <c r="AM53" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN53" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO53" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP53" t="str">
+        <v>Digital line counter / DTT warning</v>
       </c>
     </row>
     <row r="54">
@@ -9537,13 +9696,13 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>240/12 / 210/14 / 170/17</v>
+        <v>12/240 / 14/210 / 17/170</v>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>290/20 / 225/30 / 165/50</v>
+        <v>20/290 / 30/225 / 50/165</v>
       </c>
       <c r="K54" t="str">
         <v/>
@@ -9561,10 +9720,10 @@
         <v>036282967748</v>
       </c>
       <c r="P54" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q54" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R54" t="str">
         <v/>
@@ -9585,7 +9744,7 @@
         <v/>
       </c>
       <c r="X54" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y54" t="str">
         <v/>
@@ -9597,7 +9756,7 @@
         <v/>
       </c>
       <c r="AB54" t="str">
-        <v/>
+        <v>船钓 / 拖钓</v>
       </c>
       <c r="AC54" t="str">
         <v/>
@@ -9621,7 +9780,7 @@
         <v/>
       </c>
       <c r="AJ54" t="str">
-        <v/>
+        <v>计数器,船钓,深水</v>
       </c>
       <c r="AK54" t="str">
         <v/>
@@ -9630,13 +9789,16 @@
         <v/>
       </c>
       <c r="AM54" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN54" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO54" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP54" t="str">
+        <v>Digital line counter / DTT warning</v>
       </c>
     </row>
     <row r="55">
@@ -9662,13 +9824,13 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>240/12 / 210/14 / 170/17</v>
+        <v>12/240 / 14/210 / 17/170</v>
       </c>
       <c r="I55" t="str">
         <v/>
       </c>
       <c r="J55" t="str">
-        <v>290/20 / 225/30 / 165/50</v>
+        <v>20/290 / 30/225 / 50/165</v>
       </c>
       <c r="K55" t="str">
         <v/>
@@ -9686,10 +9848,10 @@
         <v>036282967731</v>
       </c>
       <c r="P55" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q55" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R55" t="str">
         <v/>
@@ -9710,7 +9872,7 @@
         <v/>
       </c>
       <c r="X55" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y55" t="str">
         <v/>
@@ -9722,7 +9884,7 @@
         <v/>
       </c>
       <c r="AB55" t="str">
-        <v/>
+        <v>船钓 / 拖钓</v>
       </c>
       <c r="AC55" t="str">
         <v/>
@@ -9746,7 +9908,7 @@
         <v/>
       </c>
       <c r="AJ55" t="str">
-        <v/>
+        <v>计数器,船钓,深水</v>
       </c>
       <c r="AK55" t="str">
         <v/>
@@ -9755,13 +9917,16 @@
         <v/>
       </c>
       <c r="AM55" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN55" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO55" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP55" t="str">
+        <v>Digital line counter / DTT warning</v>
       </c>
     </row>
     <row r="56">
@@ -9787,13 +9952,13 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>135/10 / 110/12 / 95/14</v>
+        <v>10/135 / 12/110 / 14/95</v>
       </c>
       <c r="I56" t="str">
         <v/>
       </c>
       <c r="J56" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K56" t="str">
         <v/>
@@ -9811,10 +9976,10 @@
         <v>036282093119</v>
       </c>
       <c r="P56" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q56" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R56" t="str">
         <v/>
@@ -9832,7 +9997,7 @@
         <v/>
       </c>
       <c r="W56" t="str">
-        <v/>
+        <v>X-Mag 合金 / C6 碳</v>
       </c>
       <c r="X56" t="str">
         <v/>
@@ -9847,7 +10012,7 @@
         <v/>
       </c>
       <c r="AB56" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC56" t="str">
         <v/>
@@ -9871,22 +10036,25 @@
         <v/>
       </c>
       <c r="AJ56" t="str">
-        <v/>
+        <v>finesse,轻量,高端</v>
       </c>
       <c r="AK56" t="str">
-        <v/>
+        <v>约 2g+</v>
       </c>
       <c r="AL56" t="str">
         <v/>
       </c>
       <c r="AM56" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN56" t="str">
         <v/>
       </c>
       <c r="AO56" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP56" t="str">
+        <v>SLC spool / CeramiLite / IVCB-4</v>
       </c>
     </row>
     <row r="57">
@@ -9912,13 +10080,13 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>135/10 / 110/12 / 95/14</v>
+        <v>10/135 / 12/110 / 14/95</v>
       </c>
       <c r="I57" t="str">
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K57" t="str">
         <v/>
@@ -9936,10 +10104,10 @@
         <v>036282093171</v>
       </c>
       <c r="P57" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q57" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R57" t="str">
         <v/>
@@ -9957,10 +10125,10 @@
         <v/>
       </c>
       <c r="W57" t="str">
-        <v/>
+        <v>X2-Cräftic 合金 / C6 碳</v>
       </c>
       <c r="X57" t="str">
-        <v/>
+        <v>航空级铝</v>
       </c>
       <c r="Y57" t="str">
         <v/>
@@ -9972,7 +10140,7 @@
         <v/>
       </c>
       <c r="AB57" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC57" t="str">
         <v/>
@@ -9996,22 +10164,25 @@
         <v/>
       </c>
       <c r="AJ57" t="str">
-        <v/>
+        <v>轻量,全能,heavy jig</v>
       </c>
       <c r="AK57" t="str">
-        <v/>
+        <v>约 5g+</v>
       </c>
       <c r="AL57" t="str">
         <v/>
       </c>
       <c r="AM57" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN57" t="str">
         <v/>
       </c>
       <c r="AO57" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP57" t="str">
+        <v>IVCB-4 / Compact bent handle</v>
       </c>
     </row>
     <row r="58">
@@ -10037,13 +10208,13 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>135/10 / 110/12 / 95/14</v>
+        <v>10/135 / 12/110 / 14/95</v>
       </c>
       <c r="I58" t="str">
         <v/>
       </c>
       <c r="J58" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K58" t="str">
         <v/>
@@ -10061,10 +10232,10 @@
         <v>036282093188</v>
       </c>
       <c r="P58" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q58" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R58" t="str">
         <v/>
@@ -10082,10 +10253,10 @@
         <v/>
       </c>
       <c r="W58" t="str">
-        <v/>
+        <v>X2-Cräftic 合金 / C6 碳</v>
       </c>
       <c r="X58" t="str">
-        <v/>
+        <v>航空级铝</v>
       </c>
       <c r="Y58" t="str">
         <v/>
@@ -10097,7 +10268,7 @@
         <v/>
       </c>
       <c r="AB58" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC58" t="str">
         <v/>
@@ -10121,22 +10292,25 @@
         <v/>
       </c>
       <c r="AJ58" t="str">
-        <v/>
+        <v>轻量,全能,heavy jig</v>
       </c>
       <c r="AK58" t="str">
-        <v/>
+        <v>约 5g+</v>
       </c>
       <c r="AL58" t="str">
         <v/>
       </c>
       <c r="AM58" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN58" t="str">
         <v/>
       </c>
       <c r="AO58" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP58" t="str">
+        <v>IVCB-4 / Compact bent handle</v>
       </c>
     </row>
     <row r="59">
@@ -10162,13 +10336,13 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>135/10 / 110/12 / 95/14</v>
+        <v>10/135 / 12/110 / 14/95</v>
       </c>
       <c r="I59" t="str">
         <v/>
       </c>
       <c r="J59" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K59" t="str">
         <v/>
@@ -10186,10 +10360,10 @@
         <v>036282093195</v>
       </c>
       <c r="P59" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q59" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R59" t="str">
         <v/>
@@ -10207,10 +10381,10 @@
         <v/>
       </c>
       <c r="W59" t="str">
-        <v/>
+        <v>X2-Cräftic 合金 / C6 碳</v>
       </c>
       <c r="X59" t="str">
-        <v/>
+        <v>航空级铝</v>
       </c>
       <c r="Y59" t="str">
         <v/>
@@ -10222,7 +10396,7 @@
         <v/>
       </c>
       <c r="AB59" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC59" t="str">
         <v/>
@@ -10246,22 +10420,25 @@
         <v/>
       </c>
       <c r="AJ59" t="str">
-        <v/>
+        <v>轻量,全能,heavy jig</v>
       </c>
       <c r="AK59" t="str">
-        <v/>
+        <v>约 5g+</v>
       </c>
       <c r="AL59" t="str">
         <v/>
       </c>
       <c r="AM59" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN59" t="str">
         <v/>
       </c>
       <c r="AO59" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP59" t="str">
+        <v>IVCB-4 / Compact bent handle</v>
       </c>
     </row>
     <row r="60">
@@ -10287,13 +10464,13 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>135/10 / 110/12 / 95/14</v>
+        <v>10/135 / 12/110 / 14/95</v>
       </c>
       <c r="I60" t="str">
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>145/20 / 110/30 / 75/50</v>
+        <v>20/145 / 30/110 / 50/75</v>
       </c>
       <c r="K60" t="str">
         <v/>
@@ -10311,10 +10488,10 @@
         <v>036282093201</v>
       </c>
       <c r="P60" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q60" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R60" t="str">
         <v/>
@@ -10332,10 +10509,10 @@
         <v/>
       </c>
       <c r="W60" t="str">
-        <v/>
+        <v>X2-Cräftic 合金 / C6 碳</v>
       </c>
       <c r="X60" t="str">
-        <v/>
+        <v>航空级铝</v>
       </c>
       <c r="Y60" t="str">
         <v/>
@@ -10347,7 +10524,7 @@
         <v/>
       </c>
       <c r="AB60" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC60" t="str">
         <v/>
@@ -10371,22 +10548,25 @@
         <v/>
       </c>
       <c r="AJ60" t="str">
-        <v/>
+        <v>轻量,全能,heavy jig</v>
       </c>
       <c r="AK60" t="str">
-        <v/>
+        <v>约 5g+</v>
       </c>
       <c r="AL60" t="str">
         <v/>
       </c>
       <c r="AM60" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN60" t="str">
         <v/>
       </c>
       <c r="AO60" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP60" t="str">
+        <v>IVCB-4 / Compact bent handle</v>
       </c>
     </row>
     <row r="61">
@@ -10412,13 +10592,13 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>295/12 / 250/14 / 205/17</v>
+        <v>12/295 / 14/250 / 17/205</v>
       </c>
       <c r="I61" t="str">
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>380/20 / 285/30 / 200/50</v>
+        <v>20/380 / 30/285 / 50/200</v>
       </c>
       <c r="K61" t="str">
         <v/>
@@ -10436,10 +10616,10 @@
         <v>036282144859</v>
       </c>
       <c r="P61" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q61" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R61" t="str">
         <v/>
@@ -10505,13 +10685,16 @@
         <v/>
       </c>
       <c r="AM61" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN61" t="str">
         <v/>
       </c>
       <c r="AO61" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -10537,13 +10720,13 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>295/12 / 250/14 / 205/17</v>
+        <v>12/295 / 14/250 / 17/205</v>
       </c>
       <c r="I62" t="str">
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>380/20 / 285/30 / 200/50</v>
+        <v>20/380 / 30/285 / 50/200</v>
       </c>
       <c r="K62" t="str">
         <v/>
@@ -10561,10 +10744,10 @@
         <v>036282144842</v>
       </c>
       <c r="P62" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q62" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R62" t="str">
         <v/>
@@ -10630,13 +10813,16 @@
         <v/>
       </c>
       <c r="AM62" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN62" t="str">
         <v/>
       </c>
       <c r="AO62" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -10662,13 +10848,13 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I63" t="str">
         <v/>
       </c>
       <c r="J63" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K63" t="str">
         <v/>
@@ -10686,10 +10872,10 @@
         <v>36282037588</v>
       </c>
       <c r="P63" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q63" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R63" t="str">
         <v/>
@@ -10707,10 +10893,10 @@
         <v/>
       </c>
       <c r="W63" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X63" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y63" t="str">
         <v/>
@@ -10722,7 +10908,7 @@
         <v/>
       </c>
       <c r="AB63" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC63" t="str">
         <v/>
@@ -10746,22 +10932,25 @@
         <v/>
       </c>
       <c r="AJ63" t="str">
-        <v/>
+        <v>泛用,入门进阶,鲈鱼</v>
       </c>
       <c r="AK63" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL63" t="str">
         <v/>
       </c>
       <c r="AM63" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN63" t="str">
         <v/>
       </c>
       <c r="AO63" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP63" t="str">
+        <v>A-Sym body / MagTrax</v>
       </c>
     </row>
     <row r="64">
@@ -10787,13 +10976,13 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>155/10 / 130/12 / 90/15</v>
+        <v>10/155 / 12/130 / 15/90</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64" t="str">
-        <v>165/20 / 125/30 / 85/50</v>
+        <v>20/165 / 30/125 / 50/85</v>
       </c>
       <c r="K64" t="str">
         <v/>
@@ -10811,10 +11000,10 @@
         <v>36282037601</v>
       </c>
       <c r="P64" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q64" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R64" t="str">
         <v/>
@@ -10832,10 +11021,10 @@
         <v/>
       </c>
       <c r="W64" t="str">
-        <v/>
+        <v>石墨</v>
       </c>
       <c r="X64" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y64" t="str">
         <v/>
@@ -10847,7 +11036,7 @@
         <v/>
       </c>
       <c r="AB64" t="str">
-        <v/>
+        <v>淡水路亚</v>
       </c>
       <c r="AC64" t="str">
         <v/>
@@ -10871,22 +11060,25 @@
         <v/>
       </c>
       <c r="AJ64" t="str">
-        <v/>
+        <v>泛用,入门进阶,鲈鱼</v>
       </c>
       <c r="AK64" t="str">
-        <v/>
+        <v>约 7g+</v>
       </c>
       <c r="AL64" t="str">
         <v/>
       </c>
       <c r="AM64" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN64" t="str">
         <v/>
       </c>
       <c r="AO64" t="str">
         <v>baitcasting</v>
+      </c>
+      <c r="AP64" t="str">
+        <v>A-Sym body / MagTrax</v>
       </c>
     </row>
     <row r="65">
@@ -10912,13 +11104,13 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>390/10 / 320/12 / 225/17</v>
+        <v>10/390 / 12/320 / 17/225</v>
       </c>
       <c r="I65" t="str">
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>415/20 / 310/30 / 220/50</v>
+        <v>20/415 / 30/310 / 50/220</v>
       </c>
       <c r="K65" t="str">
         <v/>
@@ -10936,10 +11128,10 @@
         <v>036282107984</v>
       </c>
       <c r="P65" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q65" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R65" t="str">
         <v/>
@@ -10972,7 +11164,7 @@
         <v/>
       </c>
       <c r="AB65" t="str">
-        <v/>
+        <v>淡海水大物</v>
       </c>
       <c r="AC65" t="str">
         <v/>
@@ -10996,7 +11188,7 @@
         <v/>
       </c>
       <c r="AJ65" t="str">
-        <v/>
+        <v>striper,鼓轮,大物</v>
       </c>
       <c r="AK65" t="str">
         <v/>
@@ -11005,13 +11197,16 @@
         <v/>
       </c>
       <c r="AM65" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN65" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO65" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP65" t="str">
+        <v>6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="66">
@@ -11037,13 +11232,13 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>225/17</v>
+        <v>17/225</v>
       </c>
       <c r="I66" t="str">
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>310/30</v>
+        <v>30/310</v>
       </c>
       <c r="K66" t="str">
         <v/>
@@ -11061,10 +11256,10 @@
         <v>036282108035</v>
       </c>
       <c r="P66" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q66" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R66" t="str">
         <v/>
@@ -11082,7 +11277,7 @@
         <v/>
       </c>
       <c r="W66" t="str">
-        <v/>
+        <v>铝</v>
       </c>
       <c r="X66" t="str">
         <v/>
@@ -11097,7 +11292,7 @@
         <v/>
       </c>
       <c r="AB66" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC66" t="str">
         <v/>
@@ -11121,7 +11316,7 @@
         <v/>
       </c>
       <c r="AJ66" t="str">
-        <v/>
+        <v>carp,鼓轮,大物</v>
       </c>
       <c r="AK66" t="str">
         <v/>
@@ -11130,13 +11325,16 @@
         <v/>
       </c>
       <c r="AM66" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN66" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO66" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP66" t="str">
+        <v>6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="67">
@@ -11162,13 +11360,13 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>390/10 / 320/12 / 225/17</v>
+        <v>10/390 / 12/320 / 17/225</v>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>415/20 / 310/30 / 220/50</v>
+        <v>20/415 / 30/310 / 50/220</v>
       </c>
       <c r="K67" t="str">
         <v/>
@@ -11186,10 +11384,10 @@
         <v>036282107991</v>
       </c>
       <c r="P67" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q67" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R67" t="str">
         <v/>
@@ -11207,7 +11405,7 @@
         <v/>
       </c>
       <c r="W67" t="str">
-        <v/>
+        <v>铝</v>
       </c>
       <c r="X67" t="str">
         <v/>
@@ -11222,7 +11420,7 @@
         <v/>
       </c>
       <c r="AB67" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC67" t="str">
         <v/>
@@ -11246,7 +11444,7 @@
         <v/>
       </c>
       <c r="AJ67" t="str">
-        <v/>
+        <v>carp,鼓轮,大物</v>
       </c>
       <c r="AK67" t="str">
         <v/>
@@ -11255,13 +11453,16 @@
         <v/>
       </c>
       <c r="AM67" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN67" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO67" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP67" t="str">
+        <v>6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="68">
@@ -11287,13 +11488,13 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>390/10 / 320/12 / 225/17</v>
+        <v>10/390 / 12/320 / 17/225</v>
       </c>
       <c r="I68" t="str">
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>415/20 / 310/30 / 220/50</v>
+        <v>20/415 / 30/310 / 50/220</v>
       </c>
       <c r="K68" t="str">
         <v/>
@@ -11311,10 +11512,10 @@
         <v>036282108004</v>
       </c>
       <c r="P68" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q68" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R68" t="str">
         <v/>
@@ -11332,7 +11533,7 @@
         <v/>
       </c>
       <c r="W68" t="str">
-        <v/>
+        <v>铝</v>
       </c>
       <c r="X68" t="str">
         <v/>
@@ -11347,7 +11548,7 @@
         <v/>
       </c>
       <c r="AB68" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC68" t="str">
         <v/>
@@ -11371,7 +11572,7 @@
         <v/>
       </c>
       <c r="AJ68" t="str">
-        <v/>
+        <v>catfish,鼓轮,大物</v>
       </c>
       <c r="AK68" t="str">
         <v/>
@@ -11380,13 +11581,16 @@
         <v/>
       </c>
       <c r="AM68" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN68" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO68" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP68" t="str">
+        <v>6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="69">
@@ -11412,13 +11616,13 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>325/17 / 250/20 / 230/25</v>
+        <v>17/325 / 20/250 / 25/230</v>
       </c>
       <c r="I69" t="str">
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>515/30 / 420/40 / 360/50</v>
+        <v>30/515 / 40/420 / 50/360</v>
       </c>
       <c r="K69" t="str">
         <v/>
@@ -11436,10 +11640,10 @@
         <v>036282108011</v>
       </c>
       <c r="P69" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q69" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R69" t="str">
         <v/>
@@ -11457,7 +11661,7 @@
         <v/>
       </c>
       <c r="W69" t="str">
-        <v/>
+        <v>铝</v>
       </c>
       <c r="X69" t="str">
         <v/>
@@ -11472,7 +11676,7 @@
         <v/>
       </c>
       <c r="AB69" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC69" t="str">
         <v/>
@@ -11496,7 +11700,7 @@
         <v/>
       </c>
       <c r="AJ69" t="str">
-        <v/>
+        <v>catfish,鼓轮,大物</v>
       </c>
       <c r="AK69" t="str">
         <v/>
@@ -11505,13 +11709,16 @@
         <v/>
       </c>
       <c r="AM69" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN69" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO69" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP69" t="str">
+        <v>6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="70">
@@ -11537,13 +11744,13 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>225/17</v>
+        <v>17/225</v>
       </c>
       <c r="I70" t="str">
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>310/30</v>
+        <v>30/310</v>
       </c>
       <c r="K70" t="str">
         <v/>
@@ -11561,10 +11768,10 @@
         <v>036282108028</v>
       </c>
       <c r="P70" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q70" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R70" t="str">
         <v/>
@@ -11582,7 +11789,7 @@
         <v/>
       </c>
       <c r="W70" t="str">
-        <v/>
+        <v>铝</v>
       </c>
       <c r="X70" t="str">
         <v/>
@@ -11597,7 +11804,7 @@
         <v/>
       </c>
       <c r="AB70" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC70" t="str">
         <v/>
@@ -11621,7 +11828,7 @@
         <v/>
       </c>
       <c r="AJ70" t="str">
-        <v/>
+        <v>catfish,鼓轮,大物</v>
       </c>
       <c r="AK70" t="str">
         <v/>
@@ -11630,13 +11837,16 @@
         <v/>
       </c>
       <c r="AM70" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN70" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO70" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP70" t="str">
+        <v>6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="71">
@@ -11662,13 +11872,13 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>270/12 / 230/14 / 190/17</v>
+        <v>12/270 / 14/230 / 17/190</v>
       </c>
       <c r="I71" t="str">
         <v/>
       </c>
       <c r="J71" t="str">
-        <v>350/20 / 265/30 / 185/50</v>
+        <v>20/350 / 30/265 / 50/185</v>
       </c>
       <c r="K71" t="str">
         <v/>
@@ -11686,10 +11896,10 @@
         <v>036282334878</v>
       </c>
       <c r="P71" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q71" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R71" t="str">
         <v/>
@@ -11722,7 +11932,7 @@
         <v/>
       </c>
       <c r="AB71" t="str">
-        <v/>
+        <v>船钓 / 拖钓</v>
       </c>
       <c r="AC71" t="str">
         <v/>
@@ -11746,7 +11956,7 @@
         <v/>
       </c>
       <c r="AJ71" t="str">
-        <v/>
+        <v>计数器,拖钓,深水</v>
       </c>
       <c r="AK71" t="str">
         <v/>
@@ -11755,13 +11965,16 @@
         <v/>
       </c>
       <c r="AM71" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN71" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO71" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP71" t="str">
+        <v>Mechanical line counter / synchronized level wind</v>
       </c>
     </row>
     <row r="72">
@@ -11787,13 +12000,13 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>305/14 / 255/17 / 210/20</v>
+        <v>14/305 / 17/255 / 20/210</v>
       </c>
       <c r="I72" t="str">
         <v/>
       </c>
       <c r="J72" t="str">
-        <v>465/20 / 350/30 / 245/50</v>
+        <v>20/465 / 30/350 / 50/245</v>
       </c>
       <c r="K72" t="str">
         <v/>
@@ -11811,10 +12024,10 @@
         <v>036282334892</v>
       </c>
       <c r="P72" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q72" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R72" t="str">
         <v/>
@@ -11847,7 +12060,7 @@
         <v/>
       </c>
       <c r="AB72" t="str">
-        <v/>
+        <v>船钓 / 拖钓</v>
       </c>
       <c r="AC72" t="str">
         <v/>
@@ -11871,7 +12084,7 @@
         <v/>
       </c>
       <c r="AJ72" t="str">
-        <v/>
+        <v>计数器,拖钓,深水</v>
       </c>
       <c r="AK72" t="str">
         <v/>
@@ -11880,13 +12093,16 @@
         <v/>
       </c>
       <c r="AM72" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN72" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO72" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP72" t="str">
+        <v>Mechanical line counter / synchronized level wind</v>
       </c>
     </row>
     <row r="73">
@@ -11912,13 +12128,13 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>390/10 / 320/12 / 225/17</v>
+        <v>10/390 / 12/320 / 17/225</v>
       </c>
       <c r="I73" t="str">
         <v/>
       </c>
       <c r="J73" t="str">
-        <v>415/20 / 310/30 / 220/50</v>
+        <v>20/415 / 30/310 / 50/220</v>
       </c>
       <c r="K73" t="str">
         <v/>
@@ -11936,10 +12152,10 @@
         <v>036282354043</v>
       </c>
       <c r="P73" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q73" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R73" t="str">
         <v/>
@@ -11957,10 +12173,10 @@
         <v/>
       </c>
       <c r="W73" t="str">
-        <v/>
+        <v>铝</v>
       </c>
       <c r="X73" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y73" t="str">
         <v/>
@@ -11972,7 +12188,7 @@
         <v/>
       </c>
       <c r="AB73" t="str">
-        <v/>
+        <v>淡海水大物</v>
       </c>
       <c r="AC73" t="str">
         <v/>
@@ -11996,7 +12212,7 @@
         <v/>
       </c>
       <c r="AJ73" t="str">
-        <v/>
+        <v>远投,鼓轮,大水面</v>
       </c>
       <c r="AK73" t="str">
         <v/>
@@ -12005,13 +12221,16 @@
         <v/>
       </c>
       <c r="AM73" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN73" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO73" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP73" t="str">
+        <v>6 pin centrifugal / synchronized level wind / Carbon Matrix</v>
       </c>
     </row>
     <row r="74">
@@ -12037,13 +12256,13 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>325/17 / 250/20 / 230/25</v>
+        <v>17/325 / 20/250 / 25/230</v>
       </c>
       <c r="I74" t="str">
         <v/>
       </c>
       <c r="J74" t="str">
-        <v>515/30 / 420/40 / 360/50</v>
+        <v>30/515 / 40/420 / 50/360</v>
       </c>
       <c r="K74" t="str">
         <v/>
@@ -12061,10 +12280,10 @@
         <v>036282615267</v>
       </c>
       <c r="P74" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q74" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R74" t="str">
         <v/>
@@ -12082,10 +12301,10 @@
         <v/>
       </c>
       <c r="W74" t="str">
-        <v/>
+        <v>铝</v>
       </c>
       <c r="X74" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y74" t="str">
         <v/>
@@ -12097,7 +12316,7 @@
         <v/>
       </c>
       <c r="AB74" t="str">
-        <v/>
+        <v>淡海水大物</v>
       </c>
       <c r="AC74" t="str">
         <v/>
@@ -12121,7 +12340,7 @@
         <v/>
       </c>
       <c r="AJ74" t="str">
-        <v/>
+        <v>远投,鼓轮,大水面</v>
       </c>
       <c r="AK74" t="str">
         <v/>
@@ -12130,13 +12349,16 @@
         <v/>
       </c>
       <c r="AM74" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN74" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO74" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP74" t="str">
+        <v>6 pin centrifugal / synchronized level wind / Carbon Matrix</v>
       </c>
     </row>
     <row r="75">
@@ -12162,13 +12384,13 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>325/17 / 250/20 / 230/25</v>
+        <v>17/325 / 20/250 / 25/230</v>
       </c>
       <c r="I75" t="str">
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>515/30 / 420/40 / 360/50</v>
+        <v>30/515 / 40/420 / 50/360</v>
       </c>
       <c r="K75" t="str">
         <v/>
@@ -12186,10 +12408,10 @@
         <v>036282615281</v>
       </c>
       <c r="P75" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q75" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R75" t="str">
         <v/>
@@ -12210,7 +12432,7 @@
         <v/>
       </c>
       <c r="X75" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y75" t="str">
         <v/>
@@ -12222,7 +12444,7 @@
         <v/>
       </c>
       <c r="AB75" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC75" t="str">
         <v/>
@@ -12246,7 +12468,7 @@
         <v/>
       </c>
       <c r="AJ75" t="str">
-        <v/>
+        <v>大水面,鼓轮,大物</v>
       </c>
       <c r="AK75" t="str">
         <v/>
@@ -12255,13 +12477,16 @@
         <v/>
       </c>
       <c r="AM75" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN75" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO75" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP75" t="str">
+        <v>4 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="76">
@@ -12287,13 +12512,13 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>325/17 / 250/20 / 230/25</v>
+        <v>17/325 / 20/250 / 25/230</v>
       </c>
       <c r="I76" t="str">
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>515/30 / 420/40 / 360/50</v>
+        <v>30/515 / 40/420 / 50/360</v>
       </c>
       <c r="K76" t="str">
         <v/>
@@ -12311,10 +12536,10 @@
         <v>036282615298</v>
       </c>
       <c r="P76" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q76" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R76" t="str">
         <v/>
@@ -12335,7 +12560,7 @@
         <v/>
       </c>
       <c r="X76" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y76" t="str">
         <v/>
@@ -12347,7 +12572,7 @@
         <v/>
       </c>
       <c r="AB76" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC76" t="str">
         <v/>
@@ -12371,7 +12596,7 @@
         <v/>
       </c>
       <c r="AJ76" t="str">
-        <v/>
+        <v>大水面,鼓轮,大物</v>
       </c>
       <c r="AK76" t="str">
         <v/>
@@ -12380,13 +12605,16 @@
         <v/>
       </c>
       <c r="AM76" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN76" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO76" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP76" t="str">
+        <v>4 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="77">
@@ -12412,13 +12640,13 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>325/17 / 250/20 / 230/25</v>
+        <v>17/325 / 20/250 / 25/230</v>
       </c>
       <c r="I77" t="str">
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>515/30 / 420/40 / 360/50</v>
+        <v>30/515 / 40/420 / 50/360</v>
       </c>
       <c r="K77" t="str">
         <v/>
@@ -12436,10 +12664,10 @@
         <v>036282615274</v>
       </c>
       <c r="P77" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q77" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R77" t="str">
         <v/>
@@ -12460,7 +12688,7 @@
         <v/>
       </c>
       <c r="X77" t="str">
-        <v/>
+        <v>黄铜</v>
       </c>
       <c r="Y77" t="str">
         <v/>
@@ -12472,7 +12700,7 @@
         <v/>
       </c>
       <c r="AB77" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC77" t="str">
         <v/>
@@ -12496,7 +12724,7 @@
         <v/>
       </c>
       <c r="AJ77" t="str">
-        <v/>
+        <v>大水面,鼓轮,大物</v>
       </c>
       <c r="AK77" t="str">
         <v/>
@@ -12505,13 +12733,16 @@
         <v/>
       </c>
       <c r="AM77" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN77" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO77" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP77" t="str">
+        <v>4 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="78">
@@ -12537,13 +12768,13 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>230/14</v>
+        <v>14/230</v>
       </c>
       <c r="I78" t="str">
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>265/30</v>
+        <v>30/265</v>
       </c>
       <c r="K78" t="str">
         <v/>
@@ -12561,10 +12792,10 @@
         <v>036282596696</v>
       </c>
       <c r="P78" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q78" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R78" t="str">
         <v/>
@@ -12597,7 +12828,7 @@
         <v/>
       </c>
       <c r="AB78" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC78" t="str">
         <v/>
@@ -12621,7 +12852,7 @@
         <v/>
       </c>
       <c r="AJ78" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK78" t="str">
         <v/>
@@ -12630,13 +12861,16 @@
         <v/>
       </c>
       <c r="AM78" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN78" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO78" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP78" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="79">
@@ -12662,13 +12896,13 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>255/17</v>
+        <v>17/255</v>
       </c>
       <c r="I79" t="str">
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>350/30</v>
+        <v>30/350</v>
       </c>
       <c r="K79" t="str">
         <v/>
@@ -12686,10 +12920,10 @@
         <v>036282596719</v>
       </c>
       <c r="P79" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q79" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R79" t="str">
         <v/>
@@ -12722,7 +12956,7 @@
         <v/>
       </c>
       <c r="AB79" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC79" t="str">
         <v/>
@@ -12746,7 +12980,7 @@
         <v/>
       </c>
       <c r="AJ79" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK79" t="str">
         <v/>
@@ -12755,13 +12989,16 @@
         <v/>
       </c>
       <c r="AM79" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN79" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO79" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP79" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="80">
@@ -12787,13 +13024,13 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>255/17</v>
+        <v>17/255</v>
       </c>
       <c r="I80" t="str">
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>350/30</v>
+        <v>30/350</v>
       </c>
       <c r="K80" t="str">
         <v/>
@@ -12811,10 +13048,10 @@
         <v>036282596726</v>
       </c>
       <c r="P80" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q80" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R80" t="str">
         <v/>
@@ -12847,7 +13084,7 @@
         <v/>
       </c>
       <c r="AB80" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC80" t="str">
         <v/>
@@ -12871,7 +13108,7 @@
         <v/>
       </c>
       <c r="AJ80" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK80" t="str">
         <v/>
@@ -12880,13 +13117,16 @@
         <v/>
       </c>
       <c r="AM80" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN80" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO80" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP80" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="81">
@@ -12912,13 +13152,13 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>255/17</v>
+        <v>17/255</v>
       </c>
       <c r="I81" t="str">
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>350/30</v>
+        <v>30/350</v>
       </c>
       <c r="K81" t="str">
         <v/>
@@ -12936,10 +13176,10 @@
         <v>036282596672</v>
       </c>
       <c r="P81" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q81" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R81" t="str">
         <v/>
@@ -12972,7 +13212,7 @@
         <v/>
       </c>
       <c r="AB81" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC81" t="str">
         <v/>
@@ -12996,7 +13236,7 @@
         <v/>
       </c>
       <c r="AJ81" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK81" t="str">
         <v/>
@@ -13005,13 +13245,16 @@
         <v/>
       </c>
       <c r="AM81" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN81" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO81" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP81" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="82">
@@ -13037,13 +13280,13 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>230/14</v>
+        <v>14/230</v>
       </c>
       <c r="I82" t="str">
         <v/>
       </c>
       <c r="J82" t="str">
-        <v>265/30</v>
+        <v>30/265</v>
       </c>
       <c r="K82" t="str">
         <v/>
@@ -13061,10 +13304,10 @@
         <v>036282596733</v>
       </c>
       <c r="P82" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q82" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R82" t="str">
         <v/>
@@ -13097,7 +13340,7 @@
         <v/>
       </c>
       <c r="AB82" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC82" t="str">
         <v/>
@@ -13121,7 +13364,7 @@
         <v/>
       </c>
       <c r="AJ82" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK82" t="str">
         <v/>
@@ -13130,13 +13373,16 @@
         <v/>
       </c>
       <c r="AM82" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN82" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO82" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP82" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="83">
@@ -13162,13 +13408,13 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>255/17</v>
+        <v>17/255</v>
       </c>
       <c r="I83" t="str">
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>350/30</v>
+        <v>30/350</v>
       </c>
       <c r="K83" t="str">
         <v/>
@@ -13186,10 +13432,10 @@
         <v>036282596795</v>
       </c>
       <c r="P83" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q83" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R83" t="str">
         <v/>
@@ -13222,7 +13468,7 @@
         <v/>
       </c>
       <c r="AB83" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC83" t="str">
         <v/>
@@ -13246,7 +13492,7 @@
         <v/>
       </c>
       <c r="AJ83" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK83" t="str">
         <v/>
@@ -13255,13 +13501,16 @@
         <v/>
       </c>
       <c r="AM83" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN83" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO83" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP83" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="84">
@@ -13287,13 +13536,13 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>255/17</v>
+        <v>17/255</v>
       </c>
       <c r="I84" t="str">
         <v/>
       </c>
       <c r="J84" t="str">
-        <v>350/30</v>
+        <v>30/350</v>
       </c>
       <c r="K84" t="str">
         <v/>
@@ -13311,10 +13560,10 @@
         <v>036282596771</v>
       </c>
       <c r="P84" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q84" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R84" t="str">
         <v/>
@@ -13347,7 +13596,7 @@
         <v/>
       </c>
       <c r="AB84" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC84" t="str">
         <v/>
@@ -13371,7 +13620,7 @@
         <v/>
       </c>
       <c r="AJ84" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK84" t="str">
         <v/>
@@ -13380,13 +13629,16 @@
         <v/>
       </c>
       <c r="AM84" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN84" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO84" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP84" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="85">
@@ -13412,13 +13664,13 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>240/12</v>
+        <v>12/240</v>
       </c>
       <c r="I85" t="str">
         <v/>
       </c>
       <c r="J85" t="str">
-        <v>235/30</v>
+        <v>30/235</v>
       </c>
       <c r="K85" t="str">
         <v/>
@@ -13436,10 +13688,10 @@
         <v>036282596559</v>
       </c>
       <c r="P85" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q85" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R85" t="str">
         <v/>
@@ -13472,7 +13724,7 @@
         <v/>
       </c>
       <c r="AB85" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC85" t="str">
         <v/>
@@ -13496,7 +13748,7 @@
         <v/>
       </c>
       <c r="AJ85" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK85" t="str">
         <v/>
@@ -13505,13 +13757,16 @@
         <v/>
       </c>
       <c r="AM85" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN85" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO85" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP85" t="str">
+        <v>Carbon Matrix / 6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="86">
@@ -13537,13 +13792,13 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>240/12</v>
+        <v>12/240</v>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>235/30</v>
+        <v>30/235</v>
       </c>
       <c r="K86" t="str">
         <v/>
@@ -13561,10 +13816,10 @@
         <v>036282596566</v>
       </c>
       <c r="P86" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q86" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R86" t="str">
         <v/>
@@ -13597,7 +13852,7 @@
         <v/>
       </c>
       <c r="AB86" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC86" t="str">
         <v/>
@@ -13621,7 +13876,7 @@
         <v/>
       </c>
       <c r="AJ86" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK86" t="str">
         <v/>
@@ -13630,13 +13885,16 @@
         <v/>
       </c>
       <c r="AM86" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN86" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO86" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP86" t="str">
+        <v>Carbon Matrix / 6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="87">
@@ -13662,13 +13920,13 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>320/12</v>
+        <v>12/320</v>
       </c>
       <c r="I87" t="str">
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>310/30</v>
+        <v>30/310</v>
       </c>
       <c r="K87" t="str">
         <v/>
@@ -13686,10 +13944,10 @@
         <v>036282596573</v>
       </c>
       <c r="P87" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q87" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R87" t="str">
         <v/>
@@ -13722,7 +13980,7 @@
         <v/>
       </c>
       <c r="AB87" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC87" t="str">
         <v/>
@@ -13746,7 +14004,7 @@
         <v/>
       </c>
       <c r="AJ87" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK87" t="str">
         <v/>
@@ -13755,13 +14013,16 @@
         <v/>
       </c>
       <c r="AM87" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN87" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO87" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP87" t="str">
+        <v>Carbon Matrix / 6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="88">
@@ -13787,13 +14048,13 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>320/12</v>
+        <v>12/320</v>
       </c>
       <c r="I88" t="str">
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>310/30</v>
+        <v>30/310</v>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -13811,10 +14072,10 @@
         <v>036282596580</v>
       </c>
       <c r="P88" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q88" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R88" t="str">
         <v/>
@@ -13847,7 +14108,7 @@
         <v/>
       </c>
       <c r="AB88" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC88" t="str">
         <v/>
@@ -13871,7 +14132,7 @@
         <v/>
       </c>
       <c r="AJ88" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK88" t="str">
         <v/>
@@ -13880,13 +14141,16 @@
         <v/>
       </c>
       <c r="AM88" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN88" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO88" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP88" t="str">
+        <v>Carbon Matrix / 6 pin centrifugal / synchronized level wind</v>
       </c>
     </row>
     <row r="89">
@@ -13912,13 +14176,13 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>240/12</v>
+        <v>12/240</v>
       </c>
       <c r="I89" t="str">
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>235/30</v>
+        <v>30/235</v>
       </c>
       <c r="K89" t="str">
         <v/>
@@ -13936,10 +14200,10 @@
         <v>036282596627</v>
       </c>
       <c r="P89" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q89" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R89" t="str">
         <v/>
@@ -13972,7 +14236,7 @@
         <v/>
       </c>
       <c r="AB89" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC89" t="str">
         <v/>
@@ -13996,7 +14260,7 @@
         <v/>
       </c>
       <c r="AJ89" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK89" t="str">
         <v/>
@@ -14005,13 +14269,16 @@
         <v/>
       </c>
       <c r="AM89" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN89" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO89" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP89" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="90">
@@ -14037,13 +14304,13 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>320/12</v>
+        <v>12/320</v>
       </c>
       <c r="I90" t="str">
         <v/>
       </c>
       <c r="J90" t="str">
-        <v>310/30</v>
+        <v>30/310</v>
       </c>
       <c r="K90" t="str">
         <v/>
@@ -14061,10 +14328,10 @@
         <v>036282596634</v>
       </c>
       <c r="P90" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q90" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R90" t="str">
         <v/>
@@ -14097,7 +14364,7 @@
         <v/>
       </c>
       <c r="AB90" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC90" t="str">
         <v/>
@@ -14121,7 +14388,7 @@
         <v/>
       </c>
       <c r="AJ90" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK90" t="str">
         <v/>
@@ -14130,13 +14397,16 @@
         <v/>
       </c>
       <c r="AM90" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN90" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO90" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP90" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="91">
@@ -14162,13 +14432,13 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>320/12</v>
+        <v>12/320</v>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>310/30</v>
+        <v>30/310</v>
       </c>
       <c r="K91" t="str">
         <v/>
@@ -14186,10 +14456,10 @@
         <v>036282596641</v>
       </c>
       <c r="P91" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q91" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R91" t="str">
         <v/>
@@ -14222,7 +14492,7 @@
         <v/>
       </c>
       <c r="AB91" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC91" t="str">
         <v/>
@@ -14246,7 +14516,7 @@
         <v/>
       </c>
       <c r="AJ91" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK91" t="str">
         <v/>
@@ -14255,13 +14525,16 @@
         <v/>
       </c>
       <c r="AM91" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN91" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO91" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP91" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="92">
@@ -14287,13 +14560,13 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>240/12</v>
+        <v>12/240</v>
       </c>
       <c r="I92" t="str">
         <v/>
       </c>
       <c r="J92" t="str">
-        <v>235/30</v>
+        <v>30/235</v>
       </c>
       <c r="K92" t="str">
         <v/>
@@ -14311,10 +14584,10 @@
         <v>036282596610</v>
       </c>
       <c r="P92" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q92" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R92" t="str">
         <v/>
@@ -14347,7 +14620,7 @@
         <v/>
       </c>
       <c r="AB92" t="str">
-        <v/>
+        <v>淡水大物</v>
       </c>
       <c r="AC92" t="str">
         <v/>
@@ -14371,7 +14644,7 @@
         <v/>
       </c>
       <c r="AJ92" t="str">
-        <v/>
+        <v>鼓轮,经典,大物</v>
       </c>
       <c r="AK92" t="str">
         <v/>
@@ -14380,13 +14653,16 @@
         <v/>
       </c>
       <c r="AM92" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN92" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO92" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP92" t="str">
+        <v>Carbon Matrix / synchronized level wind</v>
       </c>
     </row>
     <row r="93">
@@ -14412,13 +14688,13 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>205/12</v>
+        <v>12/205</v>
       </c>
       <c r="I93" t="str">
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>630/30</v>
+        <v>30/630</v>
       </c>
       <c r="K93" t="str">
         <v/>
@@ -14436,10 +14712,10 @@
         <v>036282862401</v>
       </c>
       <c r="P93" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q93" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R93" t="str">
         <v/>
@@ -14472,7 +14748,7 @@
         <v/>
       </c>
       <c r="AB93" t="str">
-        <v/>
+        <v>船钓 / 拖钓</v>
       </c>
       <c r="AC93" t="str">
         <v/>
@@ -14496,7 +14772,7 @@
         <v/>
       </c>
       <c r="AJ93" t="str">
-        <v/>
+        <v>计数器,拖钓,深水</v>
       </c>
       <c r="AK93" t="str">
         <v/>
@@ -14505,13 +14781,16 @@
         <v/>
       </c>
       <c r="AM93" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN93" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO93" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP93" t="str">
+        <v>Mechanical line counter / synchronized level wind</v>
       </c>
     </row>
     <row r="94">
@@ -14537,13 +14816,13 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>245/12</v>
+        <v>12/245</v>
       </c>
       <c r="I94" t="str">
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>630/30</v>
+        <v>30/630</v>
       </c>
       <c r="K94" t="str">
         <v/>
@@ -14561,10 +14840,10 @@
         <v>036282862418</v>
       </c>
       <c r="P94" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="Q94" t="str">
-        <v>2026-04-21T13:58:33.893Z</v>
+        <v>2026-04-21T17:00:31.331Z</v>
       </c>
       <c r="R94" t="str">
         <v/>
@@ -14597,7 +14876,7 @@
         <v/>
       </c>
       <c r="AB94" t="str">
-        <v/>
+        <v>船钓 / 拖钓</v>
       </c>
       <c r="AC94" t="str">
         <v/>
@@ -14621,7 +14900,7 @@
         <v/>
       </c>
       <c r="AJ94" t="str">
-        <v/>
+        <v>计数器,拖钓,深水</v>
       </c>
       <c r="AK94" t="str">
         <v/>
@@ -14630,18 +14909,21 @@
         <v/>
       </c>
       <c r="AM94" t="str">
-        <v/>
+        <v>单摇臂</v>
       </c>
       <c r="AN94" t="str">
-        <v/>
+        <v>高</v>
       </c>
       <c r="AO94" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
+      </c>
+      <c r="AP94" t="str">
+        <v>Mechanical line counter / synchronized level wind</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AO94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AP94"/>
   </ignoredErrors>
 </worksheet>
 </file>